--- a/output/daily_ratings/france_ratings_2026-03-21.xlsx
+++ b/output/daily_ratings/france_ratings_2026-03-21.xlsx
@@ -2078,22 +2078,22 @@
         <v>0</v>
       </c>
       <c r="O24" t="n">
-        <v>0.0009410396046439564</v>
+        <v>0.0009231051078368947</v>
       </c>
       <c r="P24" t="n">
-        <v>82.37100025232506</v>
+        <v>83.48128220366726</v>
       </c>
       <c r="Q24" t="n">
         <v>-1.438970000000012</v>
       </c>
       <c r="R24" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>75.74101064400449</v>
+        <v>53.47329774165634</v>
       </c>
       <c r="T24" t="n">
-        <v>75.74101064400449</v>
+        <v>53.47329774165634</v>
       </c>
     </row>
     <row r="25">
@@ -2152,22 +2152,22 @@
         <v>1.25</v>
       </c>
       <c r="O25" t="n">
-        <v>0.0009410396046439564</v>
+        <v>0.0009231051078368947</v>
       </c>
       <c r="P25" t="n">
-        <v>77.44423507478899</v>
+        <v>78.52784837940209</v>
       </c>
       <c r="Q25" t="n">
         <v>1.867959999999982</v>
       </c>
       <c r="R25" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>74.6237719556436</v>
+        <v>52.33534422655861</v>
       </c>
       <c r="T25" t="n">
-        <v>74.6237719556436</v>
+        <v>52.33534422655861</v>
       </c>
     </row>
     <row r="26">
@@ -2226,22 +2226,22 @@
         <v>2.75</v>
       </c>
       <c r="O26" t="n">
-        <v>0.0009410396046439564</v>
+        <v>0.0009231051078368947</v>
       </c>
       <c r="P26" t="n">
-        <v>71.53211686174571</v>
+        <v>72.58372779028389</v>
       </c>
       <c r="Q26" t="n">
         <v>-1.438970000000012</v>
       </c>
       <c r="R26" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="S26" t="n">
-        <v>68.26517604643304</v>
+        <v>45.94163570241829</v>
       </c>
       <c r="T26" t="n">
-        <v>68.26517604643304</v>
+        <v>45.94163570241829</v>
       </c>
     </row>
     <row r="27">
@@ -2300,22 +2300,22 @@
         <v>2.9</v>
       </c>
       <c r="O27" t="n">
-        <v>0.0009410396046439564</v>
+        <v>0.0009231051078368947</v>
       </c>
       <c r="P27" t="n">
-        <v>70.94090504044138</v>
+        <v>71.98931573137206</v>
       </c>
       <c r="Q27" t="n">
         <v>-1.438970000000012</v>
       </c>
       <c r="R27" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="S27" t="n">
-        <v>67.85740325020187</v>
+        <v>45.5308177730053</v>
       </c>
       <c r="T27" t="n">
-        <v>67.85740325020187</v>
+        <v>45.5308177730053</v>
       </c>
     </row>
     <row r="28">
@@ -2374,22 +2374,22 @@
         <v>5.4</v>
       </c>
       <c r="O28" t="n">
-        <v>0.0009410396046439564</v>
+        <v>0.0009231051078368947</v>
       </c>
       <c r="P28" t="n">
-        <v>61.08737468536924</v>
+        <v>62.08244808284172</v>
       </c>
       <c r="Q28" t="n">
         <v>-1.438970000000012</v>
       </c>
       <c r="R28" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="S28" t="n">
-        <v>61.06118997968237</v>
+        <v>38.68385228278889</v>
       </c>
       <c r="T28" t="n">
-        <v>61.06118997968237</v>
+        <v>38.68385228278889</v>
       </c>
     </row>
     <row r="29">
@@ -2448,22 +2448,22 @@
         <v>5.5</v>
       </c>
       <c r="O29" t="n">
-        <v>0.0009410396046439564</v>
+        <v>0.0009231051078368947</v>
       </c>
       <c r="P29" t="n">
-        <v>60.69323347116636</v>
+        <v>61.68617337690051</v>
       </c>
       <c r="Q29" t="n">
         <v>-1.438970000000012</v>
       </c>
       <c r="R29" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="S29" t="n">
-        <v>60.78934144886161</v>
+        <v>38.40997366318024</v>
       </c>
       <c r="T29" t="n">
-        <v>60.78934144886161</v>
+        <v>38.40997366318024</v>
       </c>
     </row>
     <row r="30">
@@ -2522,22 +2522,22 @@
         <v>7.5</v>
       </c>
       <c r="O30" t="n">
-        <v>0.0009410396046439564</v>
+        <v>0.0009231051078368947</v>
       </c>
       <c r="P30" t="n">
-        <v>52.81040918710865</v>
+        <v>53.76067925807624</v>
       </c>
       <c r="Q30" t="n">
         <v>1.867959999999982</v>
       </c>
       <c r="R30" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="S30" t="n">
-        <v>57.63323877934486</v>
+        <v>35.21793050101759</v>
       </c>
       <c r="T30" t="n">
-        <v>57.63323877934486</v>
+        <v>35.21793050101759</v>
       </c>
     </row>
     <row r="31">
@@ -2596,22 +2596,22 @@
         <v>8.5</v>
       </c>
       <c r="O31" t="n">
-        <v>0.0009410396046439564</v>
+        <v>0.0009231051078368947</v>
       </c>
       <c r="P31" t="n">
-        <v>48.86899704507979</v>
+        <v>49.7979321986641</v>
       </c>
       <c r="Q31" t="n">
         <v>-1.438970000000012</v>
       </c>
       <c r="R31" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="S31" t="n">
-        <v>52.6338855242382</v>
+        <v>30.19361507492054</v>
       </c>
       <c r="T31" t="n">
-        <v>52.6338855242382</v>
+        <v>30.19361507492054</v>
       </c>
     </row>
     <row r="32">
@@ -2672,22 +2672,22 @@
         <v>0</v>
       </c>
       <c r="O32" t="n">
-        <v>0.0008493310618563489</v>
+        <v>0.0008284074822481103</v>
       </c>
       <c r="P32" t="n">
-        <v>101.7793694883116</v>
+        <v>101.8388445772268</v>
       </c>
       <c r="Q32" t="n">
         <v>1.867959999999982</v>
       </c>
       <c r="R32" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="S32" t="n">
-        <v>86.52487827751678</v>
+        <v>68.44634844823601</v>
       </c>
       <c r="T32" t="n">
-        <v>86.52487827751678</v>
+        <v>68.44634844823601</v>
       </c>
     </row>
     <row r="33">
@@ -2746,22 +2746,22 @@
         <v>0.25</v>
       </c>
       <c r="O33" t="n">
-        <v>0.0008493310618563489</v>
+        <v>0.0008284074822481103</v>
       </c>
       <c r="P33" t="n">
-        <v>101.1730432419278</v>
+        <v>101.2320300696712</v>
       </c>
       <c r="Q33" t="n">
         <v>1.867959999999982</v>
       </c>
       <c r="R33" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="S33" t="n">
-        <v>86.10668070431737</v>
+        <v>68.0269587743655</v>
       </c>
       <c r="T33" t="n">
-        <v>86.10668070431737</v>
+        <v>68.0269587743655</v>
       </c>
     </row>
     <row r="34">
@@ -2820,22 +2820,22 @@
         <v>0.75</v>
       </c>
       <c r="O34" t="n">
-        <v>0.0008493310618563489</v>
+        <v>0.0008284074822481103</v>
       </c>
       <c r="P34" t="n">
-        <v>99.96039074916023</v>
+        <v>100.0184010545602</v>
       </c>
       <c r="Q34" t="n">
         <v>1.867959999999982</v>
       </c>
       <c r="R34" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="S34" t="n">
-        <v>85.27028555791856</v>
+        <v>67.18817942662449</v>
       </c>
       <c r="T34" t="n">
-        <v>85.27028555791856</v>
+        <v>67.18817942662449</v>
       </c>
     </row>
     <row r="35">
@@ -2894,22 +2894,22 @@
         <v>3.75</v>
       </c>
       <c r="O35" t="n">
-        <v>0.0008493310618563489</v>
+        <v>0.0008284074822481103</v>
       </c>
       <c r="P35" t="n">
-        <v>92.68447579255468</v>
+        <v>92.73662696389371</v>
       </c>
       <c r="Q35" t="n">
         <v>1.867959999999982</v>
       </c>
       <c r="R35" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="S35" t="n">
-        <v>80.25191467952571</v>
+        <v>62.15550334017838</v>
       </c>
       <c r="T35" t="n">
-        <v>80.25191467952571</v>
+        <v>62.15550334017838</v>
       </c>
     </row>
     <row r="36">
@@ -2968,22 +2968,22 @@
         <v>9.75</v>
       </c>
       <c r="O36" t="n">
-        <v>0.0008493310618563489</v>
+        <v>0.0008284074822481103</v>
       </c>
       <c r="P36" t="n">
-        <v>78.13264587934356</v>
+        <v>78.17307878256082</v>
       </c>
       <c r="Q36" t="n">
         <v>1.867959999999982</v>
       </c>
       <c r="R36" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="S36" t="n">
-        <v>70.21517292274</v>
+        <v>52.09015116728619</v>
       </c>
       <c r="T36" t="n">
-        <v>70.21517292274</v>
+        <v>52.09015116728619</v>
       </c>
     </row>
     <row r="37">
@@ -3042,22 +3042,22 @@
         <v>10.75</v>
       </c>
       <c r="O37" t="n">
-        <v>0.0008493310618563489</v>
+        <v>0.0008284074822481103</v>
       </c>
       <c r="P37" t="n">
-        <v>75.70734089380838</v>
+        <v>75.74582075233867</v>
       </c>
       <c r="Q37" t="n">
         <v>-2.541280000000015</v>
       </c>
       <c r="R37" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="S37" t="n">
-        <v>65.50122536741056</v>
+        <v>47.36522016512351</v>
       </c>
       <c r="T37" t="n">
-        <v>65.50122536741056</v>
+        <v>47.36522016512351</v>
       </c>
     </row>
     <row r="38">
@@ -3116,16 +3116,16 @@
         <v>21.75</v>
       </c>
       <c r="O38" t="n">
-        <v>0.0008493310618563489</v>
+        <v>0.0008284074822481103</v>
       </c>
       <c r="P38" t="n">
-        <v>51.15936746269938</v>
+        <v>51.17787623119374</v>
       </c>
       <c r="Q38" t="n">
         <v>1.867959999999982</v>
       </c>
       <c r="R38" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="S38" t="inlineStr"/>
       <c r="T38" t="inlineStr"/>
@@ -3186,16 +3186,16 @@
         <v>51.75</v>
       </c>
       <c r="O39" t="n">
-        <v>0.0008493310618563489</v>
+        <v>0.0008284074822481103</v>
       </c>
       <c r="P39" t="n">
-        <v>14.7797926796716</v>
+        <v>14.76900577786151</v>
       </c>
       <c r="Q39" t="n">
         <v>1.867959999999982</v>
       </c>
       <c r="R39" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="S39" t="inlineStr"/>
       <c r="T39" t="inlineStr"/>
@@ -3258,22 +3258,22 @@
         <v>0</v>
       </c>
       <c r="O40" t="n">
-        <v>0.0009410396046439564</v>
+        <v>0.0009231051078368947</v>
       </c>
       <c r="P40" t="n">
-        <v>80.17460640065369</v>
+        <v>80.27252093411509</v>
       </c>
       <c r="Q40" t="n">
         <v>1.867959999999982</v>
       </c>
       <c r="R40" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="S40" t="n">
-        <v>71.67890793130819</v>
+        <v>53.54114541394197</v>
       </c>
       <c r="T40" t="n">
-        <v>71.67890793130819</v>
+        <v>53.54114541394197</v>
       </c>
     </row>
     <row r="41">
@@ -3332,22 +3332,22 @@
         <v>1.75</v>
       </c>
       <c r="O41" t="n">
-        <v>0.0009410396046439564</v>
+        <v>0.0009231051078368947</v>
       </c>
       <c r="P41" t="n">
-        <v>76.01093897696902</v>
+        <v>76.10550060075983</v>
       </c>
       <c r="Q41" t="n">
         <v>1.867959999999982</v>
       </c>
       <c r="R41" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="S41" t="n">
-        <v>68.80712789114122</v>
+        <v>50.66117916913742</v>
       </c>
       <c r="T41" t="n">
-        <v>68.80712789114122</v>
+        <v>50.66117916913742</v>
       </c>
     </row>
     <row r="42">
@@ -3406,22 +3406,22 @@
         <v>2.25</v>
       </c>
       <c r="O42" t="n">
-        <v>0.0009410396046439564</v>
+        <v>0.0009231051078368947</v>
       </c>
       <c r="P42" t="n">
-        <v>74.8213197130591</v>
+        <v>74.91492336265833</v>
       </c>
       <c r="Q42" t="n">
         <v>1.867959999999982</v>
       </c>
       <c r="R42" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="S42" t="n">
-        <v>67.98661930823636</v>
+        <v>49.83833167062184</v>
       </c>
       <c r="T42" t="n">
-        <v>67.98661930823636</v>
+        <v>49.83833167062184</v>
       </c>
     </row>
     <row r="43">
@@ -3480,22 +3480,22 @@
         <v>2.3</v>
       </c>
       <c r="O43" t="n">
-        <v>0.0009410396046439564</v>
+        <v>0.0009231051078368947</v>
       </c>
       <c r="P43" t="n">
-        <v>74.70235778666812</v>
+        <v>74.79586563884818</v>
       </c>
       <c r="Q43" t="n">
         <v>1.867959999999982</v>
       </c>
       <c r="R43" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="S43" t="n">
-        <v>67.90456844994588</v>
+        <v>49.75604692077029</v>
       </c>
       <c r="T43" t="n">
-        <v>67.90456844994588</v>
+        <v>49.75604692077029</v>
       </c>
     </row>
     <row r="44">
@@ -3554,22 +3554,22 @@
         <v>2.55</v>
       </c>
       <c r="O44" t="n">
-        <v>0.0009410396046439564</v>
+        <v>0.0009231051078368947</v>
       </c>
       <c r="P44" t="n">
-        <v>74.10754815471316</v>
+        <v>74.20057701979742</v>
       </c>
       <c r="Q44" t="n">
         <v>1.867959999999982</v>
       </c>
       <c r="R44" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="S44" t="n">
-        <v>67.49431415849345</v>
+        <v>49.34462317151249</v>
       </c>
       <c r="T44" t="n">
-        <v>67.49431415849345</v>
+        <v>49.34462317151249</v>
       </c>
     </row>
     <row r="45">
@@ -3628,22 +3628,22 @@
         <v>7.05</v>
       </c>
       <c r="O45" t="n">
-        <v>0.0009410396046439564</v>
+        <v>0.0009231051078368947</v>
       </c>
       <c r="P45" t="n">
-        <v>63.40097477952398</v>
+        <v>63.4853818768839</v>
       </c>
       <c r="Q45" t="n">
         <v>1.867959999999982</v>
       </c>
       <c r="R45" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="S45" t="n">
-        <v>60.10973691234981</v>
+        <v>41.93899568487224</v>
       </c>
       <c r="T45" t="n">
-        <v>60.10973691234981</v>
+        <v>41.93899568487224</v>
       </c>
     </row>
     <row r="46">
@@ -3702,22 +3702,22 @@
         <v>9.050000000000001</v>
       </c>
       <c r="O46" t="n">
-        <v>0.0009410396046439564</v>
+        <v>0.0009231051078368947</v>
       </c>
       <c r="P46" t="n">
-        <v>58.64249772388435</v>
+        <v>58.72307292447788</v>
       </c>
       <c r="Q46" t="n">
         <v>1.867959999999982</v>
       </c>
       <c r="R46" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="S46" t="n">
-        <v>56.82770258073042</v>
+        <v>38.6476056908099</v>
       </c>
       <c r="T46" t="n">
-        <v>56.82770258073042</v>
+        <v>38.6476056908099</v>
       </c>
     </row>
     <row r="47">
@@ -3776,22 +3776,22 @@
         <v>9.15</v>
       </c>
       <c r="O47" t="n">
-        <v>0.0009410396046439564</v>
+        <v>0.0009231051078368947</v>
       </c>
       <c r="P47" t="n">
-        <v>58.40457387110237</v>
+        <v>58.48495747685759</v>
       </c>
       <c r="Q47" t="n">
         <v>1.867959999999982</v>
       </c>
       <c r="R47" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="S47" t="n">
-        <v>56.66360086414945</v>
+        <v>38.48303619110678</v>
       </c>
       <c r="T47" t="n">
-        <v>56.66360086414945</v>
+        <v>38.48303619110678</v>
       </c>
     </row>
     <row r="48">
@@ -3850,22 +3850,22 @@
         <v>9.9</v>
       </c>
       <c r="O48" t="n">
-        <v>0.0009410396046439564</v>
+        <v>0.0009231051078368947</v>
       </c>
       <c r="P48" t="n">
-        <v>56.62014497523751</v>
+        <v>56.69909161970533</v>
       </c>
       <c r="Q48" t="n">
         <v>1.867959999999982</v>
       </c>
       <c r="R48" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="S48" t="n">
-        <v>55.43283798979218</v>
+        <v>37.24876494333341</v>
       </c>
       <c r="T48" t="n">
-        <v>55.43283798979218</v>
+        <v>37.24876494333341</v>
       </c>
     </row>
     <row r="49">
@@ -3924,22 +3924,22 @@
         <v>9.950000000000001</v>
       </c>
       <c r="O49" t="n">
-        <v>0.0009410396046439564</v>
+        <v>0.0009231051078368947</v>
       </c>
       <c r="P49" t="n">
-        <v>56.50118304884651</v>
+        <v>56.58003389589518</v>
       </c>
       <c r="Q49" t="n">
         <v>1.867959999999982</v>
       </c>
       <c r="R49" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="S49" t="n">
-        <v>55.35078713150169</v>
+        <v>37.16648019348185</v>
       </c>
       <c r="T49" t="n">
-        <v>55.35078713150169</v>
+        <v>37.16648019348185</v>
       </c>
     </row>
     <row r="50">
@@ -3998,22 +3998,22 @@
         <v>11.95</v>
       </c>
       <c r="O50" t="n">
-        <v>0.0009410396046439564</v>
+        <v>0.0009231051078368947</v>
       </c>
       <c r="P50" t="n">
-        <v>51.74270599320688</v>
+        <v>51.81772494348917</v>
       </c>
       <c r="Q50" t="n">
         <v>1.867959999999982</v>
       </c>
       <c r="R50" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="S50" t="n">
-        <v>52.06875279988229</v>
+        <v>33.87509019941951</v>
       </c>
       <c r="T50" t="n">
-        <v>52.06875279988229</v>
+        <v>33.87509019941951</v>
       </c>
     </row>
     <row r="51">
@@ -4072,22 +4072,22 @@
         <v>12.2</v>
       </c>
       <c r="O51" t="n">
-        <v>0.0009410396046439564</v>
+        <v>0.0009231051078368947</v>
       </c>
       <c r="P51" t="n">
-        <v>51.14789636125192</v>
+        <v>51.22243632443841</v>
       </c>
       <c r="Q51" t="n">
         <v>1.867959999999982</v>
       </c>
       <c r="R51" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="S51" t="n">
-        <v>51.65849850842987</v>
+        <v>33.46366645016172</v>
       </c>
       <c r="T51" t="n">
-        <v>51.65849850842987</v>
+        <v>33.46366645016172</v>
       </c>
     </row>
     <row r="52">
@@ -4146,22 +4146,22 @@
         <v>12.35</v>
       </c>
       <c r="O52" t="n">
-        <v>0.0009410396046439564</v>
+        <v>0.0009231051078368947</v>
       </c>
       <c r="P52" t="n">
-        <v>50.79101058207895</v>
+        <v>50.86526315300796</v>
       </c>
       <c r="Q52" t="n">
         <v>1.867959999999982</v>
       </c>
       <c r="R52" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="S52" t="n">
-        <v>51.41234593355841</v>
+        <v>33.21681220060704</v>
       </c>
       <c r="T52" t="n">
-        <v>51.41234593355841</v>
+        <v>33.21681220060704</v>
       </c>
     </row>
     <row r="53">
@@ -4220,22 +4220,22 @@
         <v>19.35</v>
       </c>
       <c r="O53" t="n">
-        <v>0.0009410396046439564</v>
+        <v>0.0009231051078368947</v>
       </c>
       <c r="P53" t="n">
-        <v>34.13634088734024</v>
+        <v>34.19718181958692</v>
       </c>
       <c r="Q53" t="n">
         <v>1.867959999999982</v>
       </c>
       <c r="R53" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="S53" t="n">
-        <v>39.92522577289052</v>
+        <v>21.69694722138887</v>
       </c>
       <c r="T53" t="n">
-        <v>39.92522577289052</v>
+        <v>21.69694722138887</v>
       </c>
     </row>
     <row r="54">
@@ -4296,10 +4296,10 @@
         <v>0</v>
       </c>
       <c r="O54" t="n">
-        <v>-0.0004138040321987015</v>
+        <v>-0.000429352893105066</v>
       </c>
       <c r="P54" t="n">
-        <v>127.9971218489627</v>
+        <v>127.8502779632542</v>
       </c>
       <c r="Q54" t="n">
         <v>1.867959999999982</v>
@@ -4308,10 +4308,10 @@
         <v>0</v>
       </c>
       <c r="S54" t="n">
-        <v>100.3969575494159</v>
+        <v>86.42371456068361</v>
       </c>
       <c r="T54" t="n">
-        <v>100.3969575494159</v>
+        <v>86.42371456068361</v>
       </c>
     </row>
     <row r="55">
@@ -4370,10 +4370,10 @@
         <v>2</v>
       </c>
       <c r="O55" t="n">
-        <v>-0.0004138040321987015</v>
+        <v>-0.000429352893105066</v>
       </c>
       <c r="P55" t="n">
-        <v>123.6467077086957</v>
+        <v>123.5150480269212</v>
       </c>
       <c r="Q55" t="n">
         <v>5.174889999999976</v>
@@ -4382,10 +4382,10 @@
         <v>0</v>
       </c>
       <c r="S55" t="n">
-        <v>99.67724182255371</v>
+        <v>85.71302229876484</v>
       </c>
       <c r="T55" t="n">
-        <v>99.67724182255371</v>
+        <v>85.71302229876484</v>
       </c>
     </row>
     <row r="56">
@@ -4444,10 +4444,10 @@
         <v>2.5</v>
       </c>
       <c r="O56" t="n">
-        <v>-0.0004138040321987015</v>
+        <v>-0.000429352893105066</v>
       </c>
       <c r="P56" t="n">
-        <v>122.559104173629</v>
+        <v>122.4312405428379</v>
       </c>
       <c r="Q56" t="n">
         <v>5.174889999999976</v>
@@ -4456,10 +4456,10 @@
         <v>0</v>
       </c>
       <c r="S56" t="n">
-        <v>98.92709590411347</v>
+        <v>84.96396692578253</v>
       </c>
       <c r="T56" t="n">
-        <v>98.92709590411347</v>
+        <v>84.96396692578253</v>
       </c>
     </row>
     <row r="57">
@@ -4518,10 +4518,10 @@
         <v>3</v>
       </c>
       <c r="O57" t="n">
-        <v>-0.0004138040321987015</v>
+        <v>-0.000429352893105066</v>
       </c>
       <c r="P57" t="n">
-        <v>121.4715006385622</v>
+        <v>121.3474330587547</v>
       </c>
       <c r="Q57" t="n">
         <v>-8.052830000000014</v>
@@ -4530,10 +4530,10 @@
         <v>0</v>
       </c>
       <c r="S57" t="n">
-        <v>89.05347819807774</v>
+        <v>75.07279463275827</v>
       </c>
       <c r="T57" t="n">
-        <v>89.05347819807774</v>
+        <v>75.07279463275827</v>
       </c>
     </row>
     <row r="58">
@@ -4592,10 +4592,10 @@
         <v>3.5</v>
       </c>
       <c r="O58" t="n">
-        <v>-0.0004138040321987015</v>
+        <v>-0.000429352893105066</v>
       </c>
       <c r="P58" t="n">
-        <v>120.3838971034954</v>
+        <v>120.2636255746714</v>
       </c>
       <c r="Q58" t="n">
         <v>5.174889999999976</v>
@@ -4604,10 +4604,10 @@
         <v>0</v>
       </c>
       <c r="S58" t="n">
-        <v>97.42680406723294</v>
+        <v>83.46585617981791</v>
       </c>
       <c r="T58" t="n">
-        <v>97.42680406723294</v>
+        <v>83.46585617981791</v>
       </c>
     </row>
     <row r="59">
@@ -4666,10 +4666,10 @@
         <v>3.6</v>
       </c>
       <c r="O59" t="n">
-        <v>-0.0004138040321987015</v>
+        <v>-0.000429352893105066</v>
       </c>
       <c r="P59" t="n">
-        <v>120.1663763964821</v>
+        <v>120.0468640778548</v>
       </c>
       <c r="Q59" t="n">
         <v>-2.541280000000015</v>
@@ -4678,10 +4678,10 @@
         <v>0</v>
       </c>
       <c r="S59" t="n">
-        <v>91.9547496741142</v>
+        <v>77.98314356853029</v>
       </c>
       <c r="T59" t="n">
-        <v>91.9547496741142</v>
+        <v>77.98314356853029</v>
       </c>
     </row>
     <row r="60">
@@ -4740,10 +4740,10 @@
         <v>3.85</v>
       </c>
       <c r="O60" t="n">
-        <v>-0.0004138040321987015</v>
+        <v>-0.000429352893105066</v>
       </c>
       <c r="P60" t="n">
-        <v>119.6225746289487</v>
+        <v>119.5049603358132</v>
       </c>
       <c r="Q60" t="n">
         <v>-1.438970000000012</v>
@@ -4752,10 +4752,10 @@
         <v>0</v>
       </c>
       <c r="S60" t="n">
-        <v>92.33996603052702</v>
+        <v>78.37045895870931</v>
       </c>
       <c r="T60" t="n">
-        <v>92.33996603052702</v>
+        <v>78.37045895870931</v>
       </c>
     </row>
     <row r="61">
@@ -4814,10 +4814,10 @@
         <v>3.95</v>
       </c>
       <c r="O61" t="n">
-        <v>-0.0004138040321987015</v>
+        <v>-0.000429352893105066</v>
       </c>
       <c r="P61" t="n">
-        <v>119.4050539219353</v>
+        <v>119.2881988389965</v>
       </c>
       <c r="Q61" t="n">
         <v>-0.3366600000000091</v>
@@ -4826,10 +4826,10 @@
         <v>0</v>
       </c>
       <c r="S61" t="n">
-        <v>92.95022616247192</v>
+        <v>78.98249096078301</v>
       </c>
       <c r="T61" t="n">
-        <v>92.95022616247192</v>
+        <v>78.98249096078301</v>
       </c>
     </row>
     <row r="62">
@@ -4888,10 +4888,10 @@
         <v>4.45</v>
       </c>
       <c r="O62" t="n">
-        <v>-0.0004138040321987015</v>
+        <v>-0.000429352893105066</v>
       </c>
       <c r="P62" t="n">
-        <v>118.3174503868686</v>
+        <v>118.2043913549133</v>
       </c>
       <c r="Q62" t="n">
         <v>4.072579999999988</v>
@@ -4900,10 +4900,10 @@
         <v>0</v>
       </c>
       <c r="S62" t="n">
-        <v>95.24123750656349</v>
+        <v>81.28080789448136</v>
       </c>
       <c r="T62" t="n">
-        <v>95.24123750656349</v>
+        <v>81.28080789448136</v>
       </c>
     </row>
     <row r="63">
@@ -4962,10 +4962,10 @@
         <v>5.2</v>
       </c>
       <c r="O63" t="n">
-        <v>-0.0004138040321987015</v>
+        <v>-0.000429352893105066</v>
       </c>
       <c r="P63" t="n">
-        <v>116.6860450842685</v>
+        <v>116.5786801287884</v>
       </c>
       <c r="Q63" t="n">
         <v>-2.541280000000015</v>
@@ -4974,10 +4974,10 @@
         <v>0</v>
       </c>
       <c r="S63" t="n">
-        <v>89.55428273510535</v>
+        <v>75.5861663749869</v>
       </c>
       <c r="T63" t="n">
-        <v>89.55428273510535</v>
+        <v>75.5861663749869</v>
       </c>
     </row>
     <row r="64">
@@ -5036,10 +5036,10 @@
         <v>5.95</v>
       </c>
       <c r="O64" t="n">
-        <v>-0.0004138040321987015</v>
+        <v>-0.000429352893105066</v>
       </c>
       <c r="P64" t="n">
-        <v>115.0546397816683</v>
+        <v>114.9529689026635</v>
       </c>
       <c r="Q64" t="n">
         <v>5.174889999999976</v>
@@ -5048,10 +5048,10 @@
         <v>0</v>
       </c>
       <c r="S64" t="n">
-        <v>93.75108906687564</v>
+        <v>79.79548485220457</v>
       </c>
       <c r="T64" t="n">
-        <v>93.75108906687564</v>
+        <v>79.79548485220457</v>
       </c>
     </row>
     <row r="65">
@@ -5110,10 +5110,10 @@
         <v>15.95</v>
       </c>
       <c r="O65" t="n">
-        <v>-0.0004138040321987015</v>
+        <v>-0.000429352893105066</v>
       </c>
       <c r="P65" t="n">
-        <v>93.30256908033319</v>
+        <v>93.27681922099845</v>
       </c>
       <c r="Q65" t="n">
         <v>6.277199999999993</v>
@@ -5122,10 +5122,10 @@
         <v>0</v>
       </c>
       <c r="S65" t="n">
-        <v>79.50846001370331</v>
+        <v>65.57622046922849</v>
       </c>
       <c r="T65" t="n">
-        <v>79.50846001370331</v>
+        <v>65.57622046922849</v>
       </c>
     </row>
     <row r="66">
@@ -5184,10 +5184,10 @@
         <v>17.45</v>
       </c>
       <c r="O66" t="n">
-        <v>-0.0004138040321987015</v>
+        <v>-0.000429352893105066</v>
       </c>
       <c r="P66" t="n">
-        <v>90.03975847513291</v>
+        <v>90.02539676874869</v>
       </c>
       <c r="Q66" t="n">
         <v>5.174889999999976</v>
@@ -5196,10 +5196,10 @@
         <v>0</v>
       </c>
       <c r="S66" t="n">
-        <v>76.49773294274955</v>
+        <v>62.56721127361138</v>
       </c>
       <c r="T66" t="n">
-        <v>76.49773294274955</v>
+        <v>62.56721127361138</v>
       </c>
     </row>
     <row r="67">
@@ -5258,10 +5258,10 @@
         <v>19.95</v>
       </c>
       <c r="O67" t="n">
-        <v>-0.0004138040321987015</v>
+        <v>-0.000429352893105066</v>
       </c>
       <c r="P67" t="n">
-        <v>84.60174079979913</v>
+        <v>84.60635934833243</v>
       </c>
       <c r="Q67" t="n">
         <v>-8.052830000000014</v>
@@ -5270,10 +5270,10 @@
         <v>0</v>
       </c>
       <c r="S67" t="n">
-        <v>63.62353156295278</v>
+        <v>49.67981748865788</v>
       </c>
       <c r="T67" t="n">
-        <v>63.62353156295278</v>
+        <v>49.67981748865788</v>
       </c>
     </row>
     <row r="68">
@@ -5332,10 +5332,10 @@
         <v>23.95</v>
       </c>
       <c r="O68" t="n">
-        <v>-0.0004138040321987015</v>
+        <v>-0.000429352893105066</v>
       </c>
       <c r="P68" t="n">
-        <v>80.19334604495282</v>
+        <v>80.21321635076438</v>
       </c>
       <c r="Q68" t="n">
         <v>5.174889999999976</v>
@@ -5402,10 +5402,10 @@
         <v>25.45</v>
       </c>
       <c r="O69" t="n">
-        <v>-0.0004138040321987015</v>
+        <v>-0.000429352893105066</v>
       </c>
       <c r="P69" t="n">
-        <v>78.56194074235268</v>
+        <v>78.58750512463951</v>
       </c>
       <c r="Q69" t="n">
         <v>0.7656499999999937</v>
@@ -5474,10 +5474,10 @@
         <v>0</v>
       </c>
       <c r="O70" t="n">
-        <v>-0.0005190671900934398</v>
+        <v>-0.0005346160509998044</v>
       </c>
       <c r="P70" t="n">
-        <v>130.2747990461776</v>
+        <v>130.1198385688173</v>
       </c>
       <c r="Q70" t="n">
         <v>4.072579999999988</v>
@@ -5486,10 +5486,10 @@
         <v>0</v>
       </c>
       <c r="S70" t="n">
-        <v>103.4249773544123</v>
+        <v>89.51596947819334</v>
       </c>
       <c r="T70" t="n">
-        <v>103.4249773544123</v>
+        <v>89.51596947819334</v>
       </c>
     </row>
     <row r="71">
@@ -5548,10 +5548,10 @@
         <v>1.75</v>
       </c>
       <c r="O71" t="n">
-        <v>-0.0005190671900934398</v>
+        <v>-0.0005346160509998044</v>
       </c>
       <c r="P71" t="n">
-        <v>126.4552587998738</v>
+        <v>126.3136296229746</v>
       </c>
       <c r="Q71" t="n">
         <v>2.970269999999999</v>
@@ -5560,10 +5560,10 @@
         <v>0</v>
       </c>
       <c r="S71" t="n">
-        <v>100.0302606636355</v>
+        <v>86.12352889832506</v>
       </c>
       <c r="T71" t="n">
-        <v>100.0302606636355</v>
+        <v>86.12352889832506</v>
       </c>
     </row>
     <row r="72">
@@ -5622,10 +5622,10 @@
         <v>3.25</v>
       </c>
       <c r="O72" t="n">
-        <v>-0.0005190671900934398</v>
+        <v>-0.0005346160509998044</v>
       </c>
       <c r="P72" t="n">
-        <v>123.1813671601848</v>
+        <v>123.0511648122523</v>
       </c>
       <c r="Q72" t="n">
         <v>-0.3366600000000091</v>
@@ -5634,10 +5634,10 @@
         <v>0</v>
       </c>
       <c r="S72" t="n">
-        <v>95.49131210947044</v>
+        <v>81.58320180843049</v>
       </c>
       <c r="T72" t="n">
-        <v>95.49131210947044</v>
+        <v>81.58320180843049</v>
       </c>
     </row>
     <row r="73">
@@ -5696,10 +5696,10 @@
         <v>3.75</v>
       </c>
       <c r="O73" t="n">
-        <v>-0.0005190671900934398</v>
+        <v>-0.0005346160509998044</v>
       </c>
       <c r="P73" t="n">
-        <v>122.0900699469552</v>
+        <v>121.9636765420115</v>
       </c>
       <c r="Q73" t="n">
         <v>6.277199999999993</v>
@@ -5708,10 +5708,10 @@
         <v>0</v>
       </c>
       <c r="S73" t="n">
-        <v>99.30035446751279</v>
+        <v>85.40266098182342</v>
       </c>
       <c r="T73" t="n">
-        <v>99.30035446751279</v>
+        <v>85.40266098182342</v>
       </c>
     </row>
     <row r="74">
@@ -5770,10 +5770,10 @@
         <v>5.25</v>
       </c>
       <c r="O74" t="n">
-        <v>-0.0005190671900934398</v>
+        <v>-0.0005346160509998044</v>
       </c>
       <c r="P74" t="n">
-        <v>118.8161783072662</v>
+        <v>118.7012117312891</v>
       </c>
       <c r="Q74" t="n">
         <v>-1.438970000000012</v>
@@ -5782,10 +5782,10 @@
         <v>0</v>
       </c>
       <c r="S74" t="n">
-        <v>91.7202486508159</v>
+        <v>77.81496158524818</v>
       </c>
       <c r="T74" t="n">
-        <v>91.7202486508159</v>
+        <v>77.81496158524818</v>
       </c>
     </row>
     <row r="75">
@@ -5844,10 +5844,10 @@
         <v>5.3</v>
       </c>
       <c r="O75" t="n">
-        <v>-0.0005190671900934398</v>
+        <v>-0.0005346160509998044</v>
       </c>
       <c r="P75" t="n">
-        <v>118.7070485859432</v>
+        <v>118.5924629042651</v>
       </c>
       <c r="Q75" t="n">
         <v>1.867959999999982</v>
@@ -5856,10 +5856,10 @@
         <v>0</v>
       </c>
       <c r="S75" t="n">
-        <v>93.92584724413923</v>
+        <v>80.02533088659587</v>
       </c>
       <c r="T75" t="n">
-        <v>93.92584724413923</v>
+        <v>80.02533088659587</v>
       </c>
     </row>
     <row r="76">
@@ -5918,10 +5918,10 @@
         <v>6.8</v>
       </c>
       <c r="O76" t="n">
-        <v>-0.0005190671900934398</v>
+        <v>-0.0005346160509998044</v>
       </c>
       <c r="P76" t="n">
-        <v>115.4331569462542</v>
+        <v>115.3299980935427</v>
       </c>
       <c r="Q76" t="n">
         <v>6.277199999999993</v>
@@ -5930,10 +5930,10 @@
         <v>0</v>
       </c>
       <c r="S76" t="n">
-        <v>94.70892389940487</v>
+        <v>80.81790533339243</v>
       </c>
       <c r="T76" t="n">
-        <v>94.70892389940487</v>
+        <v>80.81790533339243</v>
       </c>
     </row>
     <row r="77">
@@ -5992,10 +5992,10 @@
         <v>6.85</v>
       </c>
       <c r="O77" t="n">
-        <v>-0.0005190671900934398</v>
+        <v>-0.0005346160509998044</v>
       </c>
       <c r="P77" t="n">
-        <v>115.3240272249313</v>
+        <v>115.2212492665187</v>
       </c>
       <c r="Q77" t="n">
         <v>4.072579999999988</v>
@@ -6004,10 +6004,10 @@
         <v>0</v>
       </c>
       <c r="S77" t="n">
-        <v>93.11307591456341</v>
+        <v>79.2190592513893</v>
       </c>
       <c r="T77" t="n">
-        <v>93.11307591456341</v>
+        <v>79.2190592513893</v>
       </c>
     </row>
     <row r="78">
@@ -6066,10 +6066,10 @@
         <v>8.1</v>
       </c>
       <c r="O78" t="n">
-        <v>-0.0005190671900934398</v>
+        <v>-0.0005346160509998044</v>
       </c>
       <c r="P78" t="n">
-        <v>112.5957841918571</v>
+        <v>112.5025285909167</v>
       </c>
       <c r="Q78" t="n">
         <v>4.072579999999988</v>
@@ -6078,10 +6078,10 @@
         <v>0</v>
       </c>
       <c r="S78" t="n">
-        <v>91.23134207517494</v>
+        <v>77.34006103481921</v>
       </c>
       <c r="T78" t="n">
-        <v>91.23134207517494</v>
+        <v>77.34006103481921</v>
       </c>
     </row>
     <row r="79">
@@ -6140,10 +6140,10 @@
         <v>8.25</v>
       </c>
       <c r="O79" t="n">
-        <v>-0.0005190671900934398</v>
+        <v>-0.0005346160509998044</v>
       </c>
       <c r="P79" t="n">
-        <v>112.2683950278882</v>
+        <v>112.1762821098445</v>
       </c>
       <c r="Q79" t="n">
         <v>2.970269999999999</v>
@@ -6152,10 +6152,10 @@
         <v>0</v>
       </c>
       <c r="S79" t="n">
-        <v>90.24524469881537</v>
+        <v>76.35273817216066</v>
       </c>
       <c r="T79" t="n">
-        <v>90.24524469881537</v>
+        <v>76.35273817216066</v>
       </c>
     </row>
     <row r="80">
@@ -6214,10 +6214,10 @@
         <v>9</v>
       </c>
       <c r="O80" t="n">
-        <v>-0.0005190671900934398</v>
+        <v>-0.0005346160509998044</v>
       </c>
       <c r="P80" t="n">
-        <v>110.6314492080437</v>
+        <v>110.5450497044833</v>
       </c>
       <c r="Q80" t="n">
         <v>6.277199999999993</v>
@@ -6226,10 +6226,10 @@
         <v>0</v>
       </c>
       <c r="S80" t="n">
-        <v>91.39707234208113</v>
+        <v>77.51086847222909</v>
       </c>
       <c r="T80" t="n">
-        <v>91.39707234208113</v>
+        <v>77.51086847222909</v>
       </c>
     </row>
     <row r="81">
@@ -6288,10 +6288,10 @@
         <v>9.5</v>
       </c>
       <c r="O81" t="n">
-        <v>-0.0005190671900934398</v>
+        <v>-0.0005346160509998044</v>
       </c>
       <c r="P81" t="n">
-        <v>109.5401519948141</v>
+        <v>109.4575614342425</v>
       </c>
       <c r="Q81" t="n">
         <v>4.072579999999988</v>
@@ -6300,10 +6300,10 @@
         <v>0</v>
       </c>
       <c r="S81" t="n">
-        <v>89.12380017505983</v>
+        <v>75.23558303226073</v>
       </c>
       <c r="T81" t="n">
-        <v>89.12380017505983</v>
+        <v>75.23558303226073</v>
       </c>
     </row>
     <row r="82">
@@ -6362,10 +6362,10 @@
         <v>12</v>
       </c>
       <c r="O82" t="n">
-        <v>-0.0005190671900934398</v>
+        <v>-0.0005346160509998044</v>
       </c>
       <c r="P82" t="n">
-        <v>104.0836659286658</v>
+        <v>104.0201200830386</v>
       </c>
       <c r="Q82" t="n">
         <v>0.7656499999999937</v>
@@ -6374,10 +6374,10 @@
         <v>0</v>
       </c>
       <c r="S82" t="n">
-        <v>83.07946454938399</v>
+        <v>69.19205736911009</v>
       </c>
       <c r="T82" t="n">
-        <v>83.07946454938399</v>
+        <v>69.19205736911009</v>
       </c>
     </row>
     <row r="83">
@@ -6436,10 +6436,10 @@
         <v>12.25</v>
       </c>
       <c r="O83" t="n">
-        <v>-0.0005190671900934398</v>
+        <v>-0.0005346160509998044</v>
       </c>
       <c r="P83" t="n">
-        <v>103.5380173220509</v>
+        <v>103.4763759479183</v>
       </c>
       <c r="Q83" t="n">
         <v>1.867959999999982</v>
@@ -6448,10 +6448,10 @@
         <v>0</v>
       </c>
       <c r="S83" t="n">
-        <v>83.46340709713922</v>
+        <v>69.57810080246622</v>
       </c>
       <c r="T83" t="n">
-        <v>83.46340709713922</v>
+        <v>69.57810080246622</v>
       </c>
     </row>
     <row r="84">
@@ -6510,10 +6510,10 @@
         <v>14.75</v>
       </c>
       <c r="O84" t="n">
-        <v>-0.0005190671900934398</v>
+        <v>-0.0005346160509998044</v>
       </c>
       <c r="P84" t="n">
-        <v>98.08153125590263</v>
+        <v>98.03893459671437</v>
       </c>
       <c r="Q84" t="n">
         <v>0.7656499999999937</v>
@@ -6522,10 +6522,10 @@
         <v>0</v>
       </c>
       <c r="S84" t="n">
-        <v>78.9396501027293</v>
+        <v>65.0582612926559</v>
       </c>
       <c r="T84" t="n">
-        <v>78.9396501027293</v>
+        <v>65.0582612926559</v>
       </c>
     </row>
     <row r="85">
@@ -6584,10 +6584,10 @@
         <v>24.75</v>
       </c>
       <c r="O85" t="n">
-        <v>-0.0005190671900934398</v>
+        <v>-0.0005346160509998044</v>
       </c>
       <c r="P85" t="n">
-        <v>81.43471710152609</v>
+        <v>81.45008736606616</v>
       </c>
       <c r="Q85" t="n">
         <v>0.7656499999999937</v>
@@ -6656,10 +6656,10 @@
         <v>0</v>
       </c>
       <c r="O86" t="n">
-        <v>0.0009410396046439564</v>
+        <v>0.0009231051078368947</v>
       </c>
       <c r="P86" t="n">
-        <v>73.93666690853179</v>
+        <v>73.96538011392242</v>
       </c>
       <c r="Q86" t="n">
         <v>-0.3366600000000091</v>
@@ -6668,10 +6668,10 @@
         <v>0</v>
       </c>
       <c r="S86" t="n">
-        <v>62.40725625744091</v>
+        <v>47.65838461966801</v>
       </c>
       <c r="T86" t="n">
-        <v>62.40725625744091</v>
+        <v>47.65838461966801</v>
       </c>
     </row>
     <row r="87">
@@ -6730,10 +6730,10 @@
         <v>0.15</v>
       </c>
       <c r="O87" t="n">
-        <v>0.0009410396046439564</v>
+        <v>0.0009231051078368947</v>
       </c>
       <c r="P87" t="n">
-        <v>73.63614025258379</v>
+        <v>73.66387040703449</v>
       </c>
       <c r="Q87" t="n">
         <v>-0.3366600000000091</v>
@@ -6742,10 +6742,10 @@
         <v>0</v>
       </c>
       <c r="S87" t="n">
-        <v>62.19997590474505</v>
+        <v>47.45000124045399</v>
       </c>
       <c r="T87" t="n">
-        <v>62.19997590474505</v>
+        <v>47.45000124045399</v>
       </c>
     </row>
     <row r="88">
@@ -6804,10 +6804,10 @@
         <v>0.4</v>
       </c>
       <c r="O88" t="n">
-        <v>0.0009410396046439564</v>
+        <v>0.0009231051078368947</v>
       </c>
       <c r="P88" t="n">
-        <v>73.13526249267044</v>
+        <v>73.16135422888794</v>
       </c>
       <c r="Q88" t="n">
         <v>-0.3366600000000091</v>
@@ -6816,10 +6816,10 @@
         <v>0</v>
       </c>
       <c r="S88" t="n">
-        <v>61.85450865025196</v>
+        <v>47.1026956084306</v>
       </c>
       <c r="T88" t="n">
-        <v>61.85450865025196</v>
+        <v>47.1026956084306</v>
       </c>
     </row>
     <row r="89">
@@ -6878,10 +6878,10 @@
         <v>0.5</v>
       </c>
       <c r="O89" t="n">
-        <v>0.0009410396046439564</v>
+        <v>0.0009231051078368947</v>
       </c>
       <c r="P89" t="n">
-        <v>72.9349113887051</v>
+        <v>72.96034775762932</v>
       </c>
       <c r="Q89" t="n">
         <v>2.970269999999999</v>
@@ -6890,10 +6890,10 @@
         <v>0</v>
       </c>
       <c r="S89" t="n">
-        <v>63.9971896953536</v>
+        <v>49.24930258563173</v>
       </c>
       <c r="T89" t="n">
-        <v>63.9971896953536</v>
+        <v>49.24930258563173</v>
       </c>
     </row>
     <row r="90">
@@ -6952,10 +6952,10 @@
         <v>0.6</v>
       </c>
       <c r="O90" t="n">
-        <v>0.0009410396046439564</v>
+        <v>0.0009231051078368947</v>
       </c>
       <c r="P90" t="n">
-        <v>72.73456028473976</v>
+        <v>72.7593412863707</v>
       </c>
       <c r="Q90" t="n">
         <v>-0.3366600000000091</v>
@@ -6964,10 +6964,10 @@
         <v>0</v>
       </c>
       <c r="S90" t="n">
-        <v>61.57813484665748</v>
+        <v>46.82485110281188</v>
       </c>
       <c r="T90" t="n">
-        <v>61.57813484665748</v>
+        <v>46.82485110281188</v>
       </c>
     </row>
     <row r="91">
@@ -7026,10 +7026,10 @@
         <v>1.1</v>
       </c>
       <c r="O91" t="n">
-        <v>0.0009410396046439564</v>
+        <v>0.0009231051078368947</v>
       </c>
       <c r="P91" t="n">
-        <v>71.73280476491307</v>
+        <v>71.75430893007758</v>
       </c>
       <c r="Q91" t="n">
         <v>-0.3366600000000091</v>
@@ -7038,10 +7038,10 @@
         <v>0</v>
       </c>
       <c r="S91" t="n">
-        <v>60.88720033767129</v>
+        <v>46.13023983876511</v>
       </c>
       <c r="T91" t="n">
-        <v>60.88720033767129</v>
+        <v>46.13023983876511</v>
       </c>
     </row>
     <row r="92">
@@ -7100,10 +7100,10 @@
         <v>4.6</v>
       </c>
       <c r="O92" t="n">
-        <v>0.0009410396046439564</v>
+        <v>0.0009231051078368947</v>
       </c>
       <c r="P92" t="n">
-        <v>64.7205161261262</v>
+        <v>64.71908243602586</v>
       </c>
       <c r="Q92" t="n">
         <v>-0.3366600000000091</v>
@@ -7112,10 +7112,10 @@
         <v>0</v>
       </c>
       <c r="S92" t="n">
-        <v>56.05065877476791</v>
+        <v>41.26796099043768</v>
       </c>
       <c r="T92" t="n">
-        <v>56.05065877476791</v>
+        <v>41.26796099043768</v>
       </c>
     </row>
     <row r="93">
@@ -7174,10 +7174,10 @@
         <v>5.85</v>
       </c>
       <c r="O93" t="n">
-        <v>0.0009410396046439564</v>
+        <v>0.0009231051078368947</v>
       </c>
       <c r="P93" t="n">
-        <v>62.21612732655947</v>
+        <v>62.20650154529309</v>
       </c>
       <c r="Q93" t="n">
         <v>2.970269999999999</v>
@@ -7186,10 +7186,10 @@
         <v>0</v>
       </c>
       <c r="S93" t="n">
-        <v>56.6041904492013</v>
+        <v>41.81696206033123</v>
       </c>
       <c r="T93" t="n">
-        <v>56.6041904492013</v>
+        <v>41.81696206033123</v>
       </c>
     </row>
     <row r="94">
@@ -7248,10 +7248,10 @@
         <v>7.1</v>
       </c>
       <c r="O94" t="n">
-        <v>0.0009410396046439564</v>
+        <v>0.0009231051078368947</v>
       </c>
       <c r="P94" t="n">
-        <v>59.71173852699273</v>
+        <v>59.69392065456033</v>
       </c>
       <c r="Q94" t="n">
         <v>-0.3366600000000091</v>
@@ -7260,10 +7260,10 @@
         <v>0</v>
       </c>
       <c r="S94" t="n">
-        <v>52.59598622983694</v>
+        <v>37.79490467020379</v>
       </c>
       <c r="T94" t="n">
-        <v>52.59598622983694</v>
+        <v>37.79490467020379</v>
       </c>
     </row>
     <row r="95">
@@ -7324,10 +7324,10 @@
         <v>0</v>
       </c>
       <c r="O95" t="n">
-        <v>0.0004195749107485059</v>
+        <v>0.0003721401897190705</v>
       </c>
       <c r="P95" t="n">
-        <v>110.4907076853787</v>
+        <v>111.1102301989496</v>
       </c>
       <c r="Q95" t="n">
         <v>-2.541280000000015</v>
@@ -7336,10 +7336,10 @@
         <v>0</v>
       </c>
       <c r="S95" t="n">
-        <v>85.78415931774522</v>
+        <v>71.80673888257085</v>
       </c>
       <c r="T95" t="n">
-        <v>85.78415931774522</v>
+        <v>71.80673888257085</v>
       </c>
     </row>
     <row r="96">
@@ -7398,10 +7398,10 @@
         <v>2</v>
       </c>
       <c r="O96" t="n">
-        <v>0.0004195749107485059</v>
+        <v>0.0003721401897190705</v>
       </c>
       <c r="P96" t="n">
-        <v>104.7427729008115</v>
+        <v>105.3487898948042</v>
       </c>
       <c r="Q96" t="n">
         <v>-2.541280000000015</v>
@@ -7410,10 +7410,10 @@
         <v>0</v>
       </c>
       <c r="S96" t="n">
-        <v>81.81967255480065</v>
+        <v>67.82481600483088</v>
       </c>
       <c r="T96" t="n">
-        <v>81.81967255480065</v>
+        <v>67.82481600483088</v>
       </c>
     </row>
     <row r="97">
@@ -7472,10 +7472,10 @@
         <v>2.05</v>
       </c>
       <c r="O97" t="n">
-        <v>0.0004195749107485059</v>
+        <v>0.0003721401897190705</v>
       </c>
       <c r="P97" t="n">
-        <v>104.5990745311973</v>
+        <v>105.2047538872006</v>
       </c>
       <c r="Q97" t="n">
         <v>-2.541280000000015</v>
@@ -7484,10 +7484,10 @@
         <v>0</v>
       </c>
       <c r="S97" t="n">
-        <v>81.72056038572704</v>
+        <v>67.72526793288738</v>
       </c>
       <c r="T97" t="n">
-        <v>81.72056038572704</v>
+        <v>67.72526793288738</v>
       </c>
     </row>
     <row r="98">
@@ -7546,10 +7546,10 @@
         <v>3.05</v>
       </c>
       <c r="O98" t="n">
-        <v>0.0004195749107485059</v>
+        <v>0.0003721401897190705</v>
       </c>
       <c r="P98" t="n">
-        <v>101.7251071389137</v>
+        <v>102.3240337351279</v>
       </c>
       <c r="Q98" t="n">
         <v>-2.541280000000015</v>
@@ -7558,10 +7558,10 @@
         <v>0</v>
       </c>
       <c r="S98" t="n">
-        <v>79.73831700425475</v>
+        <v>65.73430649401739</v>
       </c>
       <c r="T98" t="n">
-        <v>79.73831700425475</v>
+        <v>65.73430649401739</v>
       </c>
     </row>
     <row r="99">
@@ -7620,10 +7620,10 @@
         <v>3.8</v>
       </c>
       <c r="O99" t="n">
-        <v>0.0004195749107485059</v>
+        <v>0.0003721401897190705</v>
       </c>
       <c r="P99" t="n">
-        <v>99.56963159470105</v>
+        <v>100.1634936210734</v>
       </c>
       <c r="Q99" t="n">
         <v>-2.541280000000015</v>
@@ -7632,10 +7632,10 @@
         <v>0</v>
       </c>
       <c r="S99" t="n">
-        <v>78.25163446815054</v>
+        <v>64.2410854148649</v>
       </c>
       <c r="T99" t="n">
-        <v>78.25163446815054</v>
+        <v>64.2410854148649</v>
       </c>
     </row>
     <row r="100">
@@ -7694,10 +7694,10 @@
         <v>5.05</v>
       </c>
       <c r="O100" t="n">
-        <v>0.0004195749107485059</v>
+        <v>0.0003721401897190705</v>
       </c>
       <c r="P100" t="n">
-        <v>95.97717235434658</v>
+        <v>96.56259343098259</v>
       </c>
       <c r="Q100" t="n">
         <v>-5.848210000000009</v>
@@ -7706,10 +7706,10 @@
         <v>0</v>
       </c>
       <c r="S100" t="n">
-        <v>73.49296229441133</v>
+        <v>59.46685438626692</v>
       </c>
       <c r="T100" t="n">
-        <v>73.49296229441133</v>
+        <v>59.46685438626692</v>
       </c>
     </row>
     <row r="101">
@@ -7768,10 +7768,10 @@
         <v>5.1</v>
       </c>
       <c r="O101" t="n">
-        <v>0.0004195749107485059</v>
+        <v>0.0003721401897190705</v>
       </c>
       <c r="P101" t="n">
-        <v>95.83347398473239</v>
+        <v>96.41855742337896</v>
       </c>
       <c r="Q101" t="n">
         <v>-2.541280000000015</v>
@@ -7780,10 +7780,10 @@
         <v>0</v>
       </c>
       <c r="S101" t="n">
-        <v>75.67471807223657</v>
+        <v>61.65283554433391</v>
       </c>
       <c r="T101" t="n">
-        <v>75.67471807223657</v>
+        <v>61.65283554433391</v>
       </c>
     </row>
     <row r="102">
@@ -7842,10 +7842,10 @@
         <v>11.1</v>
       </c>
       <c r="O102" t="n">
-        <v>0.0004195749107485059</v>
+        <v>0.0003721401897190705</v>
       </c>
       <c r="P102" t="n">
-        <v>78.58966963103092</v>
+        <v>79.13423651094297</v>
       </c>
       <c r="Q102" t="n">
         <v>-5.848210000000009</v>
@@ -7854,10 +7854,10 @@
         <v>0</v>
       </c>
       <c r="S102" t="n">
-        <v>61.50038983650402</v>
+        <v>47.4215376811035</v>
       </c>
       <c r="T102" t="n">
-        <v>61.50038983650402</v>
+        <v>47.4215376811035</v>
       </c>
     </row>
     <row r="103">
@@ -7916,10 +7916,10 @@
         <v>11.35</v>
       </c>
       <c r="O103" t="n">
-        <v>0.0004195749107485059</v>
+        <v>0.0003721401897190705</v>
       </c>
       <c r="P103" t="n">
-        <v>77.87117778296002</v>
+        <v>78.41405647292481</v>
       </c>
       <c r="Q103" t="n">
         <v>4.072579999999988</v>
@@ -7928,10 +7928,10 @@
         <v>0</v>
       </c>
       <c r="S103" t="n">
-        <v>67.84743283183253</v>
+        <v>53.78038501141747</v>
       </c>
       <c r="T103" t="n">
-        <v>67.84743283183253</v>
+        <v>53.78038501141747</v>
       </c>
     </row>
     <row r="104">
@@ -7990,10 +7990,10 @@
         <v>12.1</v>
       </c>
       <c r="O104" t="n">
-        <v>0.0004195749107485059</v>
+        <v>0.0003721401897190705</v>
       </c>
       <c r="P104" t="n">
-        <v>75.71570223874734</v>
+        <v>76.25351635887031</v>
       </c>
       <c r="Q104" t="n">
         <v>-2.541280000000015</v>
@@ -8002,10 +8002,10 @@
         <v>0</v>
       </c>
       <c r="S104" t="n">
-        <v>61.79901440193061</v>
+        <v>47.716105472244</v>
       </c>
       <c r="T104" t="n">
-        <v>61.79901440193061</v>
+        <v>47.716105472244</v>
       </c>
     </row>
     <row r="105">
@@ -8064,10 +8064,10 @@
         <v>12.35</v>
       </c>
       <c r="O105" t="n">
-        <v>0.0004195749107485059</v>
+        <v>0.0003721401897190705</v>
       </c>
       <c r="P105" t="n">
-        <v>74.99721039067644</v>
+        <v>75.53333632085214</v>
       </c>
       <c r="Q105" t="n">
         <v>-5.848210000000009</v>
@@ -8076,10 +8076,10 @@
         <v>0</v>
       </c>
       <c r="S105" t="n">
-        <v>59.02258560966366</v>
+        <v>44.93283588251602</v>
       </c>
       <c r="T105" t="n">
-        <v>59.02258560966366</v>
+        <v>44.93283588251602</v>
       </c>
     </row>
     <row r="106">
@@ -8138,10 +8138,10 @@
         <v>20.35</v>
       </c>
       <c r="O106" t="n">
-        <v>0.0004195749107485059</v>
+        <v>0.0003721401897190705</v>
       </c>
       <c r="P106" t="n">
-        <v>52.51323892450587</v>
+        <v>52.99598925785921</v>
       </c>
       <c r="Q106" t="n">
         <v>-2.541280000000015</v>
@@ -8208,10 +8208,10 @@
         <v>29.35</v>
       </c>
       <c r="O107" t="n">
-        <v>0.0004195749107485059</v>
+        <v>0.0003721401897190705</v>
       </c>
       <c r="P107" t="n">
-        <v>39.58038565922976</v>
+        <v>40.03274857353222</v>
       </c>
       <c r="Q107" t="n">
         <v>-2.541280000000015</v>
@@ -8280,10 +8280,10 @@
         <v>0</v>
       </c>
       <c r="O108" t="n">
-        <v>-0.0002532777164092279</v>
+        <v>-0.0002688265773155926</v>
       </c>
       <c r="P108" t="n">
-        <v>124.5531968473706</v>
+        <v>124.4186255229149</v>
       </c>
       <c r="Q108" t="n">
         <v>-1.438970000000012</v>
@@ -8292,10 +8292,10 @@
         <v>0</v>
       </c>
       <c r="S108" t="n">
-        <v>95.83761123192539</v>
+        <v>81.76645627694892</v>
       </c>
       <c r="T108" t="n">
-        <v>95.83761123192539</v>
+        <v>81.76645627694892</v>
       </c>
     </row>
     <row r="109">
@@ -8354,10 +8354,10 @@
         <v>0.15</v>
       </c>
       <c r="O109" t="n">
-        <v>-0.0002532777164092279</v>
+        <v>-0.0002688265773155926</v>
       </c>
       <c r="P109" t="n">
-        <v>124.2285912767648</v>
+        <v>124.0951529196597</v>
       </c>
       <c r="Q109" t="n">
         <v>-2.541280000000015</v>
@@ -8366,10 +8366,10 @@
         <v>0</v>
       </c>
       <c r="S109" t="n">
-        <v>94.85343376583886</v>
+        <v>80.78105053344049</v>
       </c>
       <c r="T109" t="n">
-        <v>94.85343376583886</v>
+        <v>80.78105053344049</v>
       </c>
     </row>
     <row r="110">
@@ -8428,10 +8428,10 @@
         <v>0.9</v>
       </c>
       <c r="O110" t="n">
-        <v>-0.0002532777164092279</v>
+        <v>-0.0002688265773155926</v>
       </c>
       <c r="P110" t="n">
-        <v>122.6055634237361</v>
+        <v>122.4777899033836</v>
       </c>
       <c r="Q110" t="n">
         <v>-2.541280000000015</v>
@@ -8440,10 +8440,10 @@
         <v>0</v>
       </c>
       <c r="S110" t="n">
-        <v>93.73399301357094</v>
+        <v>79.66323719924928</v>
       </c>
       <c r="T110" t="n">
-        <v>93.73399301357094</v>
+        <v>79.66323719924928</v>
       </c>
     </row>
     <row r="111">
@@ -8502,10 +8502,10 @@
         <v>1.65</v>
       </c>
       <c r="O111" t="n">
-        <v>-0.0002532777164092279</v>
+        <v>-0.0002688265773155926</v>
       </c>
       <c r="P111" t="n">
-        <v>120.9825355707073</v>
+        <v>120.8604268871075</v>
       </c>
       <c r="Q111" t="n">
         <v>4.072579999999988</v>
@@ -8514,10 +8514,10 @@
         <v>0</v>
       </c>
       <c r="S111" t="n">
-        <v>97.17628815510076</v>
+        <v>83.11648232507905</v>
       </c>
       <c r="T111" t="n">
-        <v>97.17628815510076</v>
+        <v>83.11648232507905</v>
       </c>
     </row>
     <row r="112">
@@ -8576,10 +8576,10 @@
         <v>2.4</v>
       </c>
       <c r="O112" t="n">
-        <v>-0.0002532777164092279</v>
+        <v>-0.0002688265773155926</v>
       </c>
       <c r="P112" t="n">
-        <v>119.3595077176786</v>
+        <v>119.2430638708314</v>
       </c>
       <c r="Q112" t="n">
         <v>0.7656499999999937</v>
@@ -8588,10 +8588,10 @@
         <v>0</v>
       </c>
       <c r="S112" t="n">
-        <v>93.77597945593398</v>
+        <v>79.71313976087734</v>
       </c>
       <c r="T112" t="n">
-        <v>93.77597945593398</v>
+        <v>79.71313976087734</v>
       </c>
     </row>
     <row r="113">
@@ -8650,10 +8650,10 @@
         <v>2.45</v>
       </c>
       <c r="O113" t="n">
-        <v>-0.0002532777164092279</v>
+        <v>-0.0002688265773155926</v>
       </c>
       <c r="P113" t="n">
-        <v>119.25130586081</v>
+        <v>119.1352396697463</v>
       </c>
       <c r="Q113" t="n">
         <v>0.7656499999999937</v>
@@ -8662,10 +8662,10 @@
         <v>0</v>
       </c>
       <c r="S113" t="n">
-        <v>93.70135007244946</v>
+        <v>79.63861887193127</v>
       </c>
       <c r="T113" t="n">
-        <v>93.70135007244946</v>
+        <v>79.63861887193127</v>
       </c>
     </row>
     <row r="114">
@@ -8724,10 +8724,10 @@
         <v>2.95</v>
       </c>
       <c r="O114" t="n">
-        <v>-0.0002532777164092279</v>
+        <v>-0.0002688265773155926</v>
       </c>
       <c r="P114" t="n">
-        <v>118.1692872921242</v>
+        <v>118.0569976588956</v>
       </c>
       <c r="Q114" t="n">
         <v>2.970269999999999</v>
@@ -8736,10 +8736,10 @@
         <v>0</v>
       </c>
       <c r="S114" t="n">
-        <v>94.47563486887009</v>
+        <v>80.41709613581078</v>
       </c>
       <c r="T114" t="n">
-        <v>94.47563486887009</v>
+        <v>80.41709613581078</v>
       </c>
     </row>
     <row r="115">
@@ -8798,10 +8798,10 @@
         <v>3.7</v>
       </c>
       <c r="O115" t="n">
-        <v>-0.0002532777164092279</v>
+        <v>-0.0002688265773155926</v>
       </c>
       <c r="P115" t="n">
-        <v>116.5462594390954</v>
+        <v>116.4396346426195</v>
       </c>
       <c r="Q115" t="n">
         <v>5.174889999999976</v>
@@ -8810,10 +8810,10 @@
         <v>0</v>
       </c>
       <c r="S115" t="n">
-        <v>94.87677274786807</v>
+        <v>80.82296895495988</v>
       </c>
       <c r="T115" t="n">
-        <v>94.87677274786807</v>
+        <v>80.82296895495988</v>
       </c>
     </row>
     <row r="116">
@@ -8872,10 +8872,10 @@
         <v>4.699999999999999</v>
       </c>
       <c r="O116" t="n">
-        <v>-0.0002532777164092279</v>
+        <v>-0.0002688265773155926</v>
       </c>
       <c r="P116" t="n">
-        <v>114.3822223017238</v>
+        <v>114.283150620918</v>
       </c>
       <c r="Q116" t="n">
         <v>5.174889999999976</v>
@@ -8884,10 +8884,10 @@
         <v>0</v>
       </c>
       <c r="S116" t="n">
-        <v>93.38418507817752</v>
+        <v>79.33255117603825</v>
       </c>
       <c r="T116" t="n">
-        <v>93.38418507817752</v>
+        <v>79.33255117603825</v>
       </c>
     </row>
     <row r="117">
@@ -8946,10 +8946,10 @@
         <v>4.749999999999999</v>
       </c>
       <c r="O117" t="n">
-        <v>-0.0002532777164092279</v>
+        <v>-0.0002688265773155926</v>
       </c>
       <c r="P117" t="n">
-        <v>114.2740204448552</v>
+        <v>114.175326419833</v>
       </c>
       <c r="Q117" t="n">
         <v>-1.438970000000012</v>
@@ -8958,10 +8958,10 @@
         <v>0</v>
       </c>
       <c r="S117" t="n">
-        <v>88.74781980089527</v>
+        <v>74.6869718270712</v>
       </c>
       <c r="T117" t="n">
-        <v>88.74781980089527</v>
+        <v>74.6869718270712</v>
       </c>
     </row>
     <row r="118">
@@ -9020,10 +9020,10 @@
         <v>6.749999999999999</v>
       </c>
       <c r="O118" t="n">
-        <v>-0.0002532777164092279</v>
+        <v>-0.0002688265773155926</v>
       </c>
       <c r="P118" t="n">
-        <v>109.9459461701119</v>
+        <v>109.86235837643</v>
       </c>
       <c r="Q118" t="n">
         <v>5.174889999999976</v>
@@ -9032,10 +9032,10 @@
         <v>0</v>
       </c>
       <c r="S118" t="n">
-        <v>90.32438035531187</v>
+        <v>76.27719472924893</v>
       </c>
       <c r="T118" t="n">
-        <v>90.32438035531187</v>
+        <v>76.27719472924893</v>
       </c>
     </row>
     <row r="119">
@@ -9094,10 +9094,10 @@
         <v>7.499999999999999</v>
       </c>
       <c r="O119" t="n">
-        <v>-0.0002532777164092279</v>
+        <v>-0.0002688265773155926</v>
       </c>
       <c r="P119" t="n">
-        <v>108.3229183170832</v>
+        <v>108.2449953601539</v>
       </c>
       <c r="Q119" t="n">
         <v>6.277199999999993</v>
@@ -9106,10 +9106,10 @@
         <v>0</v>
       </c>
       <c r="S119" t="n">
-        <v>89.96522891867693</v>
+        <v>75.9212244717279</v>
       </c>
       <c r="T119" t="n">
-        <v>89.96522891867693</v>
+        <v>75.9212244717279</v>
       </c>
     </row>
     <row r="120">
@@ -9168,10 +9168,10 @@
         <v>9.5</v>
       </c>
       <c r="O120" t="n">
-        <v>-0.0002532777164092279</v>
+        <v>-0.0002688265773155926</v>
       </c>
       <c r="P120" t="n">
-        <v>103.9948440423398</v>
+        <v>103.932027316751</v>
       </c>
       <c r="Q120" t="n">
         <v>-2.541280000000015</v>
@@ -9180,10 +9180,10 @@
         <v>0</v>
       </c>
       <c r="S120" t="n">
-        <v>80.89773905423218</v>
+        <v>66.84564430052335</v>
       </c>
       <c r="T120" t="n">
-        <v>80.89773905423218</v>
+        <v>66.84564430052335</v>
       </c>
     </row>
     <row r="121">
@@ -9242,10 +9242,10 @@
         <v>10</v>
       </c>
       <c r="O121" t="n">
-        <v>-0.0002532777164092279</v>
+        <v>-0.0002688265773155926</v>
       </c>
       <c r="P121" t="n">
-        <v>102.912825473654</v>
+        <v>102.8537853059002</v>
       </c>
       <c r="Q121" t="n">
         <v>-1.438970000000012</v>
@@ -9254,10 +9254,10 @@
         <v>0</v>
       </c>
       <c r="S121" t="n">
-        <v>80.91173453501986</v>
+        <v>66.86227848773269</v>
       </c>
       <c r="T121" t="n">
-        <v>80.91173453501986</v>
+        <v>66.86227848773269</v>
       </c>
     </row>
     <row r="122">
@@ -9316,10 +9316,10 @@
         <v>40</v>
       </c>
       <c r="O122" t="n">
-        <v>-0.0002532777164092279</v>
+        <v>-0.0002688265773155926</v>
       </c>
       <c r="P122" t="n">
-        <v>59.62989031668344</v>
+        <v>59.72178599099649</v>
       </c>
       <c r="Q122" t="n">
         <v>6.277199999999993</v>
@@ -9386,10 +9386,10 @@
         <v>40.75</v>
       </c>
       <c r="O123" t="n">
-        <v>-0.0002532777164092279</v>
+        <v>-0.0002688265773155926</v>
       </c>
       <c r="P123" t="n">
-        <v>58.81837639016906</v>
+        <v>58.91310448285844</v>
       </c>
       <c r="Q123" t="n">
         <v>0.7656499999999937</v>
@@ -9458,10 +9458,10 @@
         <v>0</v>
       </c>
       <c r="O124" t="n">
-        <v>0.0009410396046439564</v>
+        <v>0.0009231051078368947</v>
       </c>
       <c r="P124" t="n">
-        <v>90.09598395774562</v>
+        <v>89.7422557737428</v>
       </c>
       <c r="Q124" t="n">
         <v>-5.848210000000009</v>
@@ -9470,10 +9470,10 @@
         <v>0</v>
       </c>
       <c r="S124" t="n">
-        <v>69.75127338770909</v>
+        <v>54.75309235496817</v>
       </c>
       <c r="T124" t="n">
-        <v>69.75127338770909</v>
+        <v>54.75309235496817</v>
       </c>
     </row>
     <row r="125">
@@ -9532,10 +9532,10 @@
         <v>0.5</v>
       </c>
       <c r="O125" t="n">
-        <v>0.0009410396046439564</v>
+        <v>0.0009231051078368947</v>
       </c>
       <c r="P125" t="n">
-        <v>89.27671042243249</v>
+        <v>88.92289517400108</v>
       </c>
       <c r="Q125" t="n">
         <v>5.174889999999976</v>
@@ -9544,10 +9544,10 @@
         <v>0</v>
       </c>
       <c r="S125" t="n">
-        <v>76.78909418192687</v>
+        <v>61.80523577944342</v>
       </c>
       <c r="T125" t="n">
-        <v>76.78909418192687</v>
+        <v>61.80523577944342</v>
       </c>
     </row>
     <row r="126">
@@ -9606,10 +9606,10 @@
         <v>0.6</v>
       </c>
       <c r="O126" t="n">
-        <v>0.0009410396046439564</v>
+        <v>0.0009231051078368947</v>
       </c>
       <c r="P126" t="n">
-        <v>89.11285571536986</v>
+        <v>88.75902305405275</v>
       </c>
       <c r="Q126" t="n">
         <v>5.174889999999976</v>
@@ -9618,10 +9618,10 @@
         <v>0</v>
       </c>
       <c r="S126" t="n">
-        <v>76.67607970950452</v>
+        <v>61.69197831099817</v>
       </c>
       <c r="T126" t="n">
-        <v>76.67607970950452</v>
+        <v>61.69197831099817</v>
       </c>
     </row>
     <row r="127">
@@ -9680,10 +9680,10 @@
         <v>0.85</v>
       </c>
       <c r="O127" t="n">
-        <v>0.0009410396046439564</v>
+        <v>0.0009231051078368947</v>
       </c>
       <c r="P127" t="n">
-        <v>88.70321894771331</v>
+        <v>88.34934275418189</v>
       </c>
       <c r="Q127" t="n">
         <v>5.174889999999976</v>
@@ -9692,10 +9692,10 @@
         <v>0</v>
       </c>
       <c r="S127" t="n">
-        <v>76.39354352844866</v>
+        <v>61.40883463988499</v>
       </c>
       <c r="T127" t="n">
-        <v>76.39354352844866</v>
+        <v>61.40883463988499</v>
       </c>
     </row>
     <row r="128">
@@ -9754,10 +9754,10 @@
         <v>1.85</v>
       </c>
       <c r="O128" t="n">
-        <v>0.0009410396046439564</v>
+        <v>0.0009231051078368947</v>
       </c>
       <c r="P128" t="n">
-        <v>87.06467187708705</v>
+        <v>86.71062155469846</v>
       </c>
       <c r="Q128" t="n">
         <v>8.481819999999999</v>
@@ -9766,10 +9766,10 @@
         <v>0</v>
       </c>
       <c r="S128" t="n">
-        <v>77.54426675112403</v>
+        <v>62.56178918544276</v>
       </c>
       <c r="T128" t="n">
-        <v>77.54426675112403</v>
+        <v>62.56178918544276</v>
       </c>
     </row>
     <row r="129">
@@ -9828,10 +9828,10 @@
         <v>2</v>
       </c>
       <c r="O129" t="n">
-        <v>0.0009410396046439564</v>
+        <v>0.0009231051078368947</v>
       </c>
       <c r="P129" t="n">
-        <v>86.81888981649311</v>
+        <v>86.46481337477594</v>
       </c>
       <c r="Q129" t="n">
         <v>5.174889999999976</v>
@@ -9840,10 +9840,10 @@
         <v>0</v>
       </c>
       <c r="S129" t="n">
-        <v>75.09387709559161</v>
+        <v>60.10637375276436</v>
       </c>
       <c r="T129" t="n">
-        <v>75.09387709559161</v>
+        <v>60.10637375276436</v>
       </c>
     </row>
     <row r="130">
@@ -9902,10 +9902,10 @@
         <v>2</v>
       </c>
       <c r="O130" t="n">
-        <v>0.0009410396046439564</v>
+        <v>0.0009231051078368947</v>
       </c>
       <c r="P130" t="n">
-        <v>86.81888981649311</v>
+        <v>86.46481337477594</v>
       </c>
       <c r="Q130" t="n">
         <v>4.072579999999988</v>
@@ -9914,10 +9914,10 @@
         <v>0</v>
       </c>
       <c r="S130" t="n">
-        <v>74.33358777995866</v>
+        <v>59.3445306760942</v>
       </c>
       <c r="T130" t="n">
-        <v>74.33358777995866</v>
+        <v>59.3445306760942</v>
       </c>
     </row>
     <row r="131">
@@ -9976,10 +9976,10 @@
         <v>3.25</v>
       </c>
       <c r="O131" t="n">
-        <v>0.0009410396046439564</v>
+        <v>0.0009231051078368947</v>
       </c>
       <c r="P131" t="n">
-        <v>84.7707059782103</v>
+        <v>84.41641187542167</v>
       </c>
       <c r="Q131" t="n">
         <v>-1.438970000000012</v>
@@ -9988,10 +9988,10 @@
         <v>0</v>
       </c>
       <c r="S131" t="n">
-        <v>69.11946029651449</v>
+        <v>54.1195969371775</v>
       </c>
       <c r="T131" t="n">
-        <v>69.11946029651449</v>
+        <v>54.1195969371775</v>
       </c>
     </row>
     <row r="132">
@@ -10050,10 +10050,10 @@
         <v>3.3</v>
       </c>
       <c r="O132" t="n">
-        <v>0.0009410396046439564</v>
+        <v>0.0009231051078368947</v>
       </c>
       <c r="P132" t="n">
-        <v>84.68877862467899</v>
+        <v>84.33447581544749</v>
       </c>
       <c r="Q132" t="n">
         <v>-10.25745000000001</v>
@@ -10062,10 +10062,10 @@
         <v>0</v>
       </c>
       <c r="S132" t="n">
-        <v>62.98063853523968</v>
+        <v>47.96822358959357</v>
       </c>
       <c r="T132" t="n">
-        <v>62.98063853523968</v>
+        <v>47.96822358959357</v>
       </c>
     </row>
     <row r="133">
@@ -10124,10 +10124,10 @@
         <v>3.55</v>
       </c>
       <c r="O133" t="n">
-        <v>0.0009410396046439564</v>
+        <v>0.0009231051078368947</v>
       </c>
       <c r="P133" t="n">
-        <v>84.27914185702242</v>
+        <v>83.92479551557665</v>
       </c>
       <c r="Q133" t="n">
         <v>1.867959999999982</v>
@@ -10136,10 +10136,10 @@
         <v>0</v>
       </c>
       <c r="S133" t="n">
-        <v>71.06128482614631</v>
+        <v>56.06535376185217</v>
       </c>
       <c r="T133" t="n">
-        <v>71.06128482614631</v>
+        <v>56.06535376185217</v>
       </c>
     </row>
     <row r="134">
@@ -10198,10 +10198,10 @@
         <v>5.55</v>
       </c>
       <c r="O134" t="n">
-        <v>0.0009410396046439564</v>
+        <v>0.0009231051078368947</v>
       </c>
       <c r="P134" t="n">
-        <v>81.00204771576992</v>
+        <v>80.64735311660979</v>
       </c>
       <c r="Q134" t="n">
         <v>0.7656499999999937</v>
@@ -10210,10 +10210,10 @@
         <v>0</v>
       </c>
       <c r="S134" t="n">
-        <v>68.04070606206633</v>
+        <v>53.03836131627659</v>
       </c>
       <c r="T134" t="n">
-        <v>68.04070606206633</v>
+        <v>53.03836131627659</v>
       </c>
     </row>
     <row r="135">
@@ -10272,10 +10272,10 @@
         <v>8.050000000000001</v>
       </c>
       <c r="O135" t="n">
-        <v>0.0009410396046439564</v>
+        <v>0.0009231051078368947</v>
       </c>
       <c r="P135" t="n">
-        <v>76.9056800392043</v>
+        <v>76.55055011790122</v>
       </c>
       <c r="Q135" t="n">
         <v>5.174889999999976</v>
@@ -10284,10 +10284,10 @@
         <v>0</v>
       </c>
       <c r="S135" t="n">
-        <v>68.25650151403937</v>
+        <v>53.25429691182543</v>
       </c>
       <c r="T135" t="n">
-        <v>68.25650151403937</v>
+        <v>53.25429691182543</v>
       </c>
     </row>
     <row r="136">
@@ -10346,10 +10346,10 @@
         <v>11.05</v>
       </c>
       <c r="O136" t="n">
-        <v>0.0009410396046439564</v>
+        <v>0.0009231051078368947</v>
       </c>
       <c r="P136" t="n">
-        <v>71.99003882732555</v>
+        <v>71.63438651945096</v>
       </c>
       <c r="Q136" t="n">
         <v>0.7656499999999937</v>
@@ -10358,10 +10358,10 @@
         <v>0</v>
       </c>
       <c r="S136" t="n">
-        <v>61.82491007883705</v>
+        <v>46.80920055178667</v>
       </c>
       <c r="T136" t="n">
-        <v>61.82491007883705</v>
+        <v>46.80920055178667</v>
       </c>
     </row>
     <row r="137">
@@ -10420,10 +10420,10 @@
         <v>15.55</v>
       </c>
       <c r="O137" t="n">
-        <v>0.0009410396046439564</v>
+        <v>0.0009231051078368947</v>
       </c>
       <c r="P137" t="n">
-        <v>64.61657700950742</v>
+        <v>64.26014112177555</v>
       </c>
       <c r="Q137" t="n">
         <v>-6.950520000000012</v>
@@ -10432,10 +10432,10 @@
         <v>0</v>
       </c>
       <c r="S137" t="n">
-        <v>51.41723361040057</v>
+        <v>36.37971293505831</v>
       </c>
       <c r="T137" t="n">
-        <v>51.41723361040057</v>
+        <v>36.37971293505831</v>
       </c>
     </row>
     <row r="138">
@@ -10499,7 +10499,7 @@
         <v>0.001857141672025071</v>
       </c>
       <c r="P138" t="n">
-        <v>116.1698753106958</v>
+        <v>116.2227684927414</v>
       </c>
       <c r="Q138" t="n">
         <v>-2.541280000000015</v>
@@ -10508,10 +10508,10 @@
         <v>0</v>
       </c>
       <c r="S138" t="n">
-        <v>89.3762025385148</v>
+        <v>75.34018401446335</v>
       </c>
       <c r="T138" t="n">
-        <v>89.3762025385148</v>
+        <v>75.34018401446335</v>
       </c>
     </row>
     <row r="139">
@@ -10573,7 +10573,7 @@
         <v>0.001857141672025071</v>
       </c>
       <c r="P139" t="n">
-        <v>116.0667331725042</v>
+        <v>116.1192889669208</v>
       </c>
       <c r="Q139" t="n">
         <v>-2.541280000000015</v>
@@ -10582,10 +10582,10 @@
         <v>0</v>
       </c>
       <c r="S139" t="n">
-        <v>89.30506296284317</v>
+        <v>75.26866587498941</v>
       </c>
       <c r="T139" t="n">
-        <v>89.30506296284317</v>
+        <v>75.26866587498941</v>
       </c>
     </row>
     <row r="140">
@@ -10647,7 +10647,7 @@
         <v>0.001857141672025071</v>
       </c>
       <c r="P140" t="n">
-        <v>115.0353117905884</v>
+        <v>115.0844937087153</v>
       </c>
       <c r="Q140" t="n">
         <v>-2.541280000000015</v>
@@ -10656,10 +10656,10 @@
         <v>0</v>
       </c>
       <c r="S140" t="n">
-        <v>88.59366720612685</v>
+        <v>74.55348448025015</v>
       </c>
       <c r="T140" t="n">
-        <v>88.59366720612685</v>
+        <v>74.55348448025015</v>
       </c>
     </row>
     <row r="141">
@@ -10721,7 +10721,7 @@
         <v>0.001857141672025071</v>
       </c>
       <c r="P141" t="n">
-        <v>113.4881797177147</v>
+        <v>113.5323008214069</v>
       </c>
       <c r="Q141" t="n">
         <v>-2.541280000000015</v>
@@ -10730,10 +10730,10 @@
         <v>0</v>
       </c>
       <c r="S141" t="n">
-        <v>87.52657357105238</v>
+        <v>73.48071238814126</v>
       </c>
       <c r="T141" t="n">
-        <v>87.52657357105238</v>
+        <v>73.48071238814126</v>
       </c>
     </row>
     <row r="142">
@@ -10797,7 +10797,7 @@
         <v>0.002159530506154391</v>
       </c>
       <c r="P142" t="n">
-        <v>109.7030334942969</v>
+        <v>109.7272417861576</v>
       </c>
       <c r="Q142" t="n">
         <v>6.277199999999993</v>
@@ -10806,10 +10806,10 @@
         <v>0</v>
       </c>
       <c r="S142" t="n">
-        <v>91.1806759641446</v>
+        <v>76.94565423973326</v>
       </c>
       <c r="T142" t="n">
-        <v>91.1806759641446</v>
+        <v>76.94565423973326</v>
       </c>
     </row>
     <row r="143">
@@ -10871,7 +10871,7 @@
         <v>0.002159530506154391</v>
       </c>
       <c r="P143" t="n">
-        <v>104.1050524675692</v>
+        <v>104.1152942448748</v>
       </c>
       <c r="Q143" t="n">
         <v>6.277199999999993</v>
@@ -10880,10 +10880,10 @@
         <v>0</v>
       </c>
       <c r="S143" t="n">
-        <v>87.31961585969381</v>
+        <v>73.06705077885346</v>
       </c>
       <c r="T143" t="n">
-        <v>87.31961585969381</v>
+        <v>73.06705077885346</v>
       </c>
     </row>
     <row r="144">
@@ -10945,7 +10945,7 @@
         <v>0.002159530506154391</v>
       </c>
       <c r="P144" t="n">
-        <v>97.38747523549578</v>
+        <v>97.38095719533551</v>
       </c>
       <c r="Q144" t="n">
         <v>-2.541280000000015</v>
@@ -10954,10 +10954,10 @@
         <v>0</v>
       </c>
       <c r="S144" t="n">
-        <v>76.60402920928921</v>
+        <v>62.31798201243639</v>
       </c>
       <c r="T144" t="n">
-        <v>76.60402920928921</v>
+        <v>62.31798201243639</v>
       </c>
     </row>
     <row r="145">
@@ -11019,7 +11019,7 @@
         <v>0.002159530506154391</v>
       </c>
       <c r="P145" t="n">
-        <v>95.14828282480467</v>
+        <v>95.13617817882241</v>
       </c>
       <c r="Q145" t="n">
         <v>6.277199999999993</v>
@@ -11028,10 +11028,10 @@
         <v>0</v>
       </c>
       <c r="S145" t="n">
-        <v>81.14191969257254</v>
+        <v>66.86128524144577</v>
       </c>
       <c r="T145" t="n">
-        <v>81.14191969257254</v>
+        <v>66.86128524144577</v>
       </c>
     </row>
     <row r="146">
@@ -11093,7 +11093,7 @@
         <v>0.002159530506154391</v>
       </c>
       <c r="P146" t="n">
-        <v>93.46888851678632</v>
+        <v>93.45259391643756</v>
       </c>
       <c r="Q146" t="n">
         <v>-2.541280000000015</v>
@@ -11102,10 +11102,10 @@
         <v>0</v>
       </c>
       <c r="S146" t="n">
-        <v>73.90128713617365</v>
+        <v>59.60295958982052</v>
       </c>
       <c r="T146" t="n">
-        <v>73.90128713617365</v>
+        <v>59.60295958982052</v>
       </c>
     </row>
     <row r="147">
@@ -11167,7 +11167,7 @@
         <v>0.002159530506154391</v>
       </c>
       <c r="P147" t="n">
-        <v>92.90909041411354</v>
+        <v>92.89139916230928</v>
       </c>
       <c r="Q147" t="n">
         <v>6.277199999999993</v>
@@ -11176,10 +11176,10 @@
         <v>0</v>
       </c>
       <c r="S147" t="n">
-        <v>79.59749565079223</v>
+        <v>65.30984385709384</v>
       </c>
       <c r="T147" t="n">
-        <v>79.59749565079223</v>
+        <v>65.30984385709384</v>
       </c>
     </row>
     <row r="148">
@@ -11241,7 +11241,7 @@
         <v>0.002159530506154391</v>
       </c>
       <c r="P148" t="n">
-        <v>85.07191697669462</v>
+        <v>85.03467260451342</v>
       </c>
       <c r="Q148" t="n">
         <v>6.277199999999993</v>
@@ -11250,10 +11250,10 @@
         <v>0</v>
       </c>
       <c r="S148" t="n">
-        <v>74.19201150456112</v>
+        <v>59.87979901186213</v>
       </c>
       <c r="T148" t="n">
-        <v>74.19201150456112</v>
+        <v>59.87979901186213</v>
       </c>
     </row>
     <row r="149">
@@ -11315,7 +11315,7 @@
         <v>0.002159530506154391</v>
       </c>
       <c r="P149" t="n">
-        <v>81.71312836065795</v>
+        <v>81.66750407974375</v>
       </c>
       <c r="Q149" t="n">
         <v>6.277199999999993</v>
@@ -11324,10 +11324,10 @@
         <v>0</v>
       </c>
       <c r="S149" t="n">
-        <v>71.87537544189065</v>
+        <v>57.55263693533423</v>
       </c>
       <c r="T149" t="n">
-        <v>71.87537544189065</v>
+        <v>57.55263693533423</v>
       </c>
     </row>
     <row r="150">
@@ -11389,7 +11389,7 @@
         <v>0.002159530506154391</v>
       </c>
       <c r="P150" t="n">
-        <v>55.42195995231743</v>
+        <v>55.31074131077767</v>
       </c>
       <c r="Q150" t="n">
         <v>6.277199999999993</v>
@@ -11461,7 +11461,7 @@
         <v>0.002094788311286708</v>
       </c>
       <c r="P151" t="n">
-        <v>111.1358709814362</v>
+        <v>111.1448384530675</v>
       </c>
       <c r="Q151" t="n">
         <v>6.277199999999993</v>
@@ -11470,10 +11470,10 @@
         <v>0</v>
       </c>
       <c r="S151" t="n">
-        <v>92.1298657427557</v>
+        <v>77.92540241057084</v>
       </c>
       <c r="T151" t="n">
-        <v>92.1298657427557</v>
+        <v>77.92540241057084</v>
       </c>
     </row>
     <row r="152">
@@ -11535,7 +11535,7 @@
         <v>0.002094788311286708</v>
       </c>
       <c r="P152" t="n">
-        <v>110.49876898931</v>
+        <v>110.5072234167394</v>
       </c>
       <c r="Q152" t="n">
         <v>6.277199999999993</v>
@@ -11544,10 +11544,10 @@
         <v>0</v>
       </c>
       <c r="S152" t="n">
-        <v>91.69044140878253</v>
+        <v>77.48472546759896</v>
       </c>
       <c r="T152" t="n">
-        <v>91.69044140878253</v>
+        <v>77.48472546759896</v>
       </c>
     </row>
     <row r="153">
@@ -11609,7 +11609,7 @@
         <v>0.002094788311286708</v>
       </c>
       <c r="P153" t="n">
-        <v>100.3051371152919</v>
+        <v>100.3053828354901</v>
       </c>
       <c r="Q153" t="n">
         <v>6.277199999999993</v>
@@ -11618,10 +11618,10 @@
         <v>0</v>
       </c>
       <c r="S153" t="n">
-        <v>84.65965206521172</v>
+        <v>70.43389438004877</v>
       </c>
       <c r="T153" t="n">
-        <v>84.65965206521172</v>
+        <v>70.43389438004877</v>
       </c>
     </row>
     <row r="154">
@@ -11683,7 +11683,7 @@
         <v>0.002094788311286708</v>
       </c>
       <c r="P154" t="n">
-        <v>96.4825251625351</v>
+        <v>96.47969261752166</v>
       </c>
       <c r="Q154" t="n">
         <v>-1.438970000000012</v>
@@ -11692,10 +11692,10 @@
         <v>0</v>
       </c>
       <c r="S154" t="n">
-        <v>76.70108085194198</v>
+        <v>62.45693118552632</v>
       </c>
       <c r="T154" t="n">
-        <v>76.70108085194198</v>
+        <v>62.45693118552632</v>
       </c>
     </row>
     <row r="155">
@@ -11757,7 +11757,7 @@
         <v>0.002094788311286708</v>
       </c>
       <c r="P155" t="n">
-        <v>90.11150524127376</v>
+        <v>90.10354225424088</v>
       </c>
       <c r="Q155" t="n">
         <v>6.277199999999993</v>
@@ -11766,10 +11766,10 @@
         <v>0</v>
       </c>
       <c r="S155" t="n">
-        <v>77.62886272164091</v>
+        <v>63.38306329249858</v>
       </c>
       <c r="T155" t="n">
-        <v>77.62886272164091</v>
+        <v>63.38306329249858</v>
       </c>
     </row>
     <row r="156">
@@ -11831,7 +11831,7 @@
         <v>0.002094788311286708</v>
       </c>
       <c r="P156" t="n">
-        <v>88.20019926489536</v>
+        <v>88.19069714525665</v>
       </c>
       <c r="Q156" t="n">
         <v>-1.438970000000012</v>
@@ -11840,10 +11840,10 @@
         <v>0</v>
       </c>
       <c r="S156" t="n">
-        <v>70.9885645102907</v>
+        <v>56.72813092689179</v>
       </c>
       <c r="T156" t="n">
-        <v>70.9885645102907</v>
+        <v>56.72813092689179</v>
       </c>
     </row>
     <row r="157">
@@ -11905,7 +11905,7 @@
         <v>0.002094788311286708</v>
       </c>
       <c r="P157" t="n">
-        <v>86.92599528064309</v>
+        <v>86.91546707260049</v>
       </c>
       <c r="Q157" t="n">
         <v>6.277199999999993</v>
@@ -11914,10 +11914,10 @@
         <v>0</v>
       </c>
       <c r="S157" t="n">
-        <v>75.43174105177503</v>
+        <v>61.17967857763915</v>
       </c>
       <c r="T157" t="n">
-        <v>75.43174105177503</v>
+        <v>61.17967857763915</v>
       </c>
     </row>
     <row r="158">
@@ -11979,7 +11979,7 @@
         <v>0.002094788311286708</v>
       </c>
       <c r="P158" t="n">
-        <v>86.67115448379263</v>
+        <v>86.66042105806926</v>
       </c>
       <c r="Q158" t="n">
         <v>-1.438970000000012</v>
@@ -11988,10 +11988,10 @@
         <v>0</v>
       </c>
       <c r="S158" t="n">
-        <v>69.93394610875507</v>
+        <v>55.67050626375926</v>
       </c>
       <c r="T158" t="n">
-        <v>69.93394610875507</v>
+        <v>55.67050626375926</v>
       </c>
     </row>
     <row r="159">
@@ -12055,7 +12055,7 @@
         <v>0.001759641672025071</v>
       </c>
       <c r="P159" t="n">
-        <v>118.2393386125888</v>
+        <v>118.2990012036163</v>
       </c>
       <c r="Q159" t="n">
         <v>-2.541280000000015</v>
@@ -12064,10 +12064,10 @@
         <v>0</v>
       </c>
       <c r="S159" t="n">
-        <v>90.74471875385838</v>
+        <v>76.77513744529148</v>
       </c>
       <c r="T159" t="n">
-        <v>90.74471875385838</v>
+        <v>76.77513744529148</v>
       </c>
     </row>
     <row r="160">
@@ -12129,7 +12129,7 @@
         <v>0.001759641672025071</v>
       </c>
       <c r="P160" t="n">
-        <v>109.9615577524895</v>
+        <v>109.9941429442449</v>
       </c>
       <c r="Q160" t="n">
         <v>-9.155140000000017</v>
@@ -12138,10 +12138,10 @@
         <v>0</v>
       </c>
       <c r="S160" t="n">
-        <v>80.47360133845194</v>
+        <v>66.46431542726133</v>
       </c>
       <c r="T160" t="n">
-        <v>80.47360133845194</v>
+        <v>66.46431542726133</v>
       </c>
     </row>
     <row r="161">
@@ -12203,7 +12203,7 @@
         <v>0.001759641672025071</v>
       </c>
       <c r="P161" t="n">
-        <v>99.61433167736537</v>
+        <v>99.61307012003073</v>
       </c>
       <c r="Q161" t="n">
         <v>-9.155140000000017</v>
@@ -12212,10 +12212,10 @@
         <v>0</v>
       </c>
       <c r="S161" t="n">
-        <v>73.33687443644106</v>
+        <v>59.28961097974987</v>
       </c>
       <c r="T161" t="n">
-        <v>73.33687443644106</v>
+        <v>59.28961097974987</v>
       </c>
     </row>
     <row r="162">
@@ -12277,7 +12277,7 @@
         <v>0.001759641672025071</v>
       </c>
       <c r="P162" t="n">
-        <v>99.09697037360917</v>
+        <v>99.09401647882002</v>
       </c>
       <c r="Q162" t="n">
         <v>-13.56438000000001</v>
@@ -12286,10 +12286,10 @@
         <v>0</v>
       </c>
       <c r="S162" t="n">
-        <v>69.93888082880871</v>
+        <v>55.88350345069365</v>
       </c>
       <c r="T162" t="n">
-        <v>69.93888082880871</v>
+        <v>55.88350345069365</v>
       </c>
     </row>
     <row r="163">
@@ -12351,7 +12351,7 @@
         <v>0.001759641672025071</v>
       </c>
       <c r="P163" t="n">
-        <v>93.92335733604709</v>
+        <v>93.90348006671292</v>
       </c>
       <c r="Q163" t="n">
         <v>-2.541280000000015</v>
@@ -12360,10 +12360,10 @@
         <v>0</v>
       </c>
       <c r="S163" t="n">
-        <v>73.97341053413281</v>
+        <v>59.91458199363954</v>
       </c>
       <c r="T163" t="n">
-        <v>73.97341053413281</v>
+        <v>59.91458199363954</v>
       </c>
     </row>
     <row r="164">
@@ -12425,7 +12425,7 @@
         <v>0.001759641672025071</v>
       </c>
       <c r="P164" t="n">
-        <v>85.64557647594778</v>
+        <v>85.59862180734154</v>
       </c>
       <c r="Q164" t="n">
         <v>-2.541280000000015</v>
@@ -12434,10 +12434,10 @@
         <v>0</v>
       </c>
       <c r="S164" t="n">
-        <v>68.26402901252412</v>
+        <v>54.17481843563036</v>
       </c>
       <c r="T164" t="n">
-        <v>68.26402901252412</v>
+        <v>54.17481843563036</v>
       </c>
     </row>
     <row r="165">
@@ -12499,7 +12499,7 @@
         <v>0.001759641672025071</v>
       </c>
       <c r="P165" t="n">
-        <v>75.05423567709886</v>
+        <v>74.97263573719543</v>
       </c>
       <c r="Q165" t="n">
         <v>-13.56438000000001</v>
@@ -12568,10 +12568,10 @@
         <v>0</v>
       </c>
       <c r="O166" t="n">
-        <v>0.0001912407464298551</v>
+        <v>0.0001960459293661945</v>
       </c>
       <c r="P166" t="n">
-        <v>79.89652725348813</v>
+        <v>79.66501911883024</v>
       </c>
       <c r="Q166" t="n">
         <v>8.481819999999999</v>
@@ -12580,10 +12580,10 @@
         <v>0</v>
       </c>
       <c r="S166" t="n">
-        <v>76.82511457537258</v>
+        <v>57.69233917887779</v>
       </c>
       <c r="T166" t="n">
-        <v>76.82511457537258</v>
+        <v>57.69233917887779</v>
       </c>
     </row>
     <row r="167">
@@ -12642,10 +12642,10 @@
         <v>0.75</v>
       </c>
       <c r="O167" t="n">
-        <v>0.0001912407464298551</v>
+        <v>0.0001960459293661945</v>
       </c>
       <c r="P167" t="n">
-        <v>78.10381766751365</v>
+        <v>77.86783686594143</v>
       </c>
       <c r="Q167" t="n">
         <v>8.481819999999999</v>
@@ -12654,10 +12654,10 @@
         <v>0</v>
       </c>
       <c r="S167" t="n">
-        <v>75.58864031291539</v>
+        <v>56.45024679390639</v>
       </c>
       <c r="T167" t="n">
-        <v>75.58864031291539</v>
+        <v>56.45024679390639</v>
       </c>
     </row>
     <row r="168">
@@ -12716,10 +12716,10 @@
         <v>0.78</v>
       </c>
       <c r="O168" t="n">
-        <v>0.0001912407464298551</v>
+        <v>0.0001960459293661945</v>
       </c>
       <c r="P168" t="n">
-        <v>78.03210928407468</v>
+        <v>77.79594957582587</v>
       </c>
       <c r="Q168" t="n">
         <v>6.277199999999993</v>
@@ -12728,10 +12728,10 @@
         <v>0</v>
       </c>
       <c r="S168" t="n">
-        <v>74.01860271115119</v>
+        <v>54.8768769451672</v>
       </c>
       <c r="T168" t="n">
-        <v>74.01860271115119</v>
+        <v>54.8768769451672</v>
       </c>
     </row>
     <row r="169">
@@ -12790,10 +12790,10 @@
         <v>0.8300000000000001</v>
       </c>
       <c r="O169" t="n">
-        <v>0.0001912407464298551</v>
+        <v>0.0001960459293661945</v>
       </c>
       <c r="P169" t="n">
-        <v>77.91259531167637</v>
+        <v>77.67613742563329</v>
       </c>
       <c r="Q169" t="n">
         <v>5.174889999999976</v>
@@ -12802,10 +12802,10 @@
         <v>0</v>
       </c>
       <c r="S169" t="n">
-        <v>73.17588177802108</v>
+        <v>54.03222770949894</v>
       </c>
       <c r="T169" t="n">
-        <v>73.17588177802108</v>
+        <v>54.03222770949894</v>
       </c>
     </row>
     <row r="170">
@@ -12864,10 +12864,10 @@
         <v>1.33</v>
       </c>
       <c r="O170" t="n">
-        <v>0.0001912407464298551</v>
+        <v>0.0001960459293661945</v>
       </c>
       <c r="P170" t="n">
-        <v>76.71745558769339</v>
+        <v>76.4780159237074</v>
       </c>
       <c r="Q170" t="n">
         <v>2.970269999999999</v>
@@ -12876,10 +12876,10 @@
         <v>0</v>
       </c>
       <c r="S170" t="n">
-        <v>70.83098697178373</v>
+        <v>51.68047996617769</v>
       </c>
       <c r="T170" t="n">
-        <v>70.83098697178373</v>
+        <v>51.68047996617769</v>
       </c>
     </row>
     <row r="171">
@@ -12938,10 +12938,10 @@
         <v>1.58</v>
       </c>
       <c r="O171" t="n">
-        <v>0.0001912407464298551</v>
+        <v>0.0001960459293661945</v>
       </c>
       <c r="P171" t="n">
-        <v>76.11988572570189</v>
+        <v>75.87895517274447</v>
       </c>
       <c r="Q171" t="n">
         <v>-6.950520000000012</v>
@@ -12950,10 +12950,10 @@
         <v>0</v>
       </c>
       <c r="S171" t="n">
-        <v>63.5762250436014</v>
+        <v>44.40986148115576</v>
       </c>
       <c r="T171" t="n">
-        <v>63.5762250436014</v>
+        <v>44.40986148115576</v>
       </c>
     </row>
     <row r="172">
@@ -13012,10 +13012,10 @@
         <v>2.08</v>
       </c>
       <c r="O172" t="n">
-        <v>0.0001912407464298551</v>
+        <v>0.0001960459293661945</v>
       </c>
       <c r="P172" t="n">
-        <v>74.92474600171892</v>
+        <v>74.68083367081859</v>
       </c>
       <c r="Q172" t="n">
         <v>-5.848210000000009</v>
@@ -13024,10 +13024,10 @@
         <v>0</v>
       </c>
       <c r="S172" t="n">
-        <v>63.51219818426291</v>
+        <v>44.34364296784499</v>
       </c>
       <c r="T172" t="n">
-        <v>63.51219818426291</v>
+        <v>44.34364296784499</v>
       </c>
     </row>
     <row r="173">
@@ -13086,10 +13086,10 @@
         <v>2.58</v>
       </c>
       <c r="O173" t="n">
-        <v>0.0001912407464298551</v>
+        <v>0.0001960459293661945</v>
       </c>
       <c r="P173" t="n">
-        <v>73.72960627773593</v>
+        <v>73.48271216889272</v>
       </c>
       <c r="Q173" t="n">
         <v>8.481819999999999</v>
@@ -13098,10 +13098,10 @@
         <v>0</v>
       </c>
       <c r="S173" t="n">
-        <v>72.57164311251988</v>
+        <v>53.41954137457616</v>
       </c>
       <c r="T173" t="n">
-        <v>72.57164311251988</v>
+        <v>53.41954137457616</v>
       </c>
     </row>
     <row r="174">
@@ -13160,10 +13160,10 @@
         <v>2.83</v>
       </c>
       <c r="O174" t="n">
-        <v>0.0001912407464298551</v>
+        <v>0.0001960459293661945</v>
       </c>
       <c r="P174" t="n">
-        <v>73.13203641574444</v>
+        <v>72.88365141792977</v>
       </c>
       <c r="Q174" t="n">
         <v>9.584129999999988</v>
@@ -13172,10 +13172,10 @@
         <v>0</v>
       </c>
       <c r="S174" t="n">
-        <v>72.9197743406671</v>
+        <v>53.76735365625584</v>
       </c>
       <c r="T174" t="n">
-        <v>72.9197743406671</v>
+        <v>53.76735365625584</v>
       </c>
     </row>
     <row r="175">
@@ -13234,10 +13234,10 @@
         <v>2.88</v>
       </c>
       <c r="O175" t="n">
-        <v>0.0001912407464298551</v>
+        <v>0.0001960459293661945</v>
       </c>
       <c r="P175" t="n">
-        <v>73.01252244334613</v>
+        <v>72.76383926773718</v>
       </c>
       <c r="Q175" t="n">
         <v>11.78874999999999</v>
@@ -13246,10 +13246,10 @@
         <v>0</v>
       </c>
       <c r="S175" t="n">
-        <v>74.35792135443586</v>
+        <v>55.20823365059808</v>
       </c>
       <c r="T175" t="n">
-        <v>74.35792135443586</v>
+        <v>55.20823365059808</v>
       </c>
     </row>
     <row r="176">
@@ -13308,10 +13308,10 @@
         <v>3.88</v>
       </c>
       <c r="O176" t="n">
-        <v>0.0001912407464298551</v>
+        <v>0.0001960459293661945</v>
       </c>
       <c r="P176" t="n">
-        <v>70.62224299538016</v>
+        <v>70.36759626388543</v>
       </c>
       <c r="Q176" t="n">
         <v>4.072579999999988</v>
@@ -13320,10 +13320,10 @@
         <v>0</v>
       </c>
       <c r="S176" t="n">
-        <v>67.38726379506225</v>
+        <v>48.21920893394507</v>
       </c>
       <c r="T176" t="n">
-        <v>67.38726379506225</v>
+        <v>48.21920893394507</v>
       </c>
     </row>
     <row r="177">
@@ -13382,10 +13382,10 @@
         <v>4.13</v>
       </c>
       <c r="O177" t="n">
-        <v>0.0001912407464298551</v>
+        <v>0.0001960459293661945</v>
       </c>
       <c r="P177" t="n">
-        <v>70.02467313338867</v>
+        <v>69.76853551292248</v>
       </c>
       <c r="Q177" t="n">
         <v>-1.438970000000012</v>
@@ -13394,10 +13394,10 @@
         <v>0</v>
       </c>
       <c r="S177" t="n">
-        <v>63.17365912941177</v>
+        <v>43.99596275560378</v>
       </c>
       <c r="T177" t="n">
-        <v>63.17365912941177</v>
+        <v>43.99596275560378</v>
       </c>
     </row>
     <row r="178">
@@ -13456,10 +13456,10 @@
         <v>4.88</v>
       </c>
       <c r="O178" t="n">
-        <v>0.0001912407464298551</v>
+        <v>0.0001960459293661945</v>
       </c>
       <c r="P178" t="n">
-        <v>68.2319635474142</v>
+        <v>67.97135326003367</v>
       </c>
       <c r="Q178" t="n">
         <v>6.277199999999993</v>
@@ -13468,10 +13468,10 @@
         <v>0</v>
       </c>
       <c r="S178" t="n">
-        <v>67.25921007638527</v>
+        <v>48.08677190732352</v>
       </c>
       <c r="T178" t="n">
-        <v>67.25921007638527</v>
+        <v>48.08677190732352</v>
       </c>
     </row>
     <row r="179">
@@ -13530,10 +13530,10 @@
         <v>5.03</v>
       </c>
       <c r="O179" t="n">
-        <v>0.0001912407464298551</v>
+        <v>0.0001960459293661945</v>
       </c>
       <c r="P179" t="n">
-        <v>67.8734216302193</v>
+        <v>67.61191680945591</v>
       </c>
       <c r="Q179" t="n">
         <v>8.481819999999999</v>
@@ -13542,10 +13542,10 @@
         <v>0</v>
       </c>
       <c r="S179" t="n">
-        <v>68.53249385515976</v>
+        <v>49.36203958366957</v>
       </c>
       <c r="T179" t="n">
-        <v>68.53249385515976</v>
+        <v>49.36203958366957</v>
       </c>
     </row>
     <row r="180">
@@ -13604,10 +13604,10 @@
         <v>8.530000000000001</v>
       </c>
       <c r="O180" t="n">
-        <v>0.0001912407464298551</v>
+        <v>0.0001960459293661945</v>
       </c>
       <c r="P180" t="n">
-        <v>59.50744356233839</v>
+        <v>59.22506629597476</v>
       </c>
       <c r="Q180" t="n">
         <v>-1.438970000000012</v>
@@ -13616,10 +13616,10 @@
         <v>0</v>
       </c>
       <c r="S180" t="n">
-        <v>55.91967678966297</v>
+        <v>36.70902076377154</v>
       </c>
       <c r="T180" t="n">
-        <v>55.91967678966297</v>
+        <v>36.70902076377154</v>
       </c>
     </row>
     <row r="181">
@@ -13680,10 +13680,10 @@
         <v>0</v>
       </c>
       <c r="O181" t="n">
-        <v>0.0001251580510831528</v>
+        <v>0.0001341677690887891</v>
       </c>
       <c r="P181" t="n">
-        <v>101.4459644732397</v>
+        <v>101.3573425006842</v>
       </c>
       <c r="Q181" t="n">
         <v>1.867959999999982</v>
@@ -13692,10 +13692,10 @@
         <v>0</v>
       </c>
       <c r="S181" t="n">
-        <v>87.08665476770807</v>
+        <v>68.11356636024234</v>
       </c>
       <c r="T181" t="n">
-        <v>87.08665476770807</v>
+        <v>68.11356636024234</v>
       </c>
     </row>
     <row r="182">
@@ -13754,10 +13754,10 @@
         <v>2</v>
       </c>
       <c r="O182" t="n">
-        <v>0.0001251580510831528</v>
+        <v>0.0001341677690887891</v>
       </c>
       <c r="P182" t="n">
-        <v>96.58348970867596</v>
+        <v>96.48273625081383</v>
       </c>
       <c r="Q182" t="n">
         <v>-9.155140000000017</v>
@@ -13766,10 +13766,10 @@
         <v>0</v>
       </c>
       <c r="S182" t="n">
-        <v>76.12999759668875</v>
+        <v>57.12613320495964</v>
       </c>
       <c r="T182" t="n">
-        <v>76.12999759668875</v>
+        <v>57.12613320495964</v>
       </c>
     </row>
     <row r="183">
@@ -13828,10 +13828,10 @@
         <v>2.25</v>
       </c>
       <c r="O183" t="n">
-        <v>0.0001251580510831528</v>
+        <v>0.0001341677690887891</v>
       </c>
       <c r="P183" t="n">
-        <v>95.9756803631055</v>
+        <v>95.87341046958005</v>
       </c>
       <c r="Q183" t="n">
         <v>6.277199999999993</v>
@@ -13840,10 +13840,10 @@
         <v>0</v>
       </c>
       <c r="S183" t="n">
-        <v>86.35482751371393</v>
+        <v>67.37081097976929</v>
       </c>
       <c r="T183" t="n">
-        <v>86.35482751371393</v>
+        <v>67.37081097976929</v>
       </c>
     </row>
     <row r="184">
@@ -13902,10 +13902,10 @@
         <v>4</v>
       </c>
       <c r="O184" t="n">
-        <v>0.0001251580510831528</v>
+        <v>0.0001341677690887891</v>
       </c>
       <c r="P184" t="n">
-        <v>91.72101494411226</v>
+        <v>91.60813000094352</v>
       </c>
       <c r="Q184" t="n">
         <v>2.970269999999999</v>
@@ -13914,10 +13914,10 @@
         <v>0</v>
       </c>
       <c r="S184" t="n">
-        <v>81.13941605396153</v>
+        <v>62.13740465975036</v>
       </c>
       <c r="T184" t="n">
-        <v>81.13941605396153</v>
+        <v>62.13740465975036</v>
       </c>
     </row>
     <row r="185">
@@ -13976,10 +13976,10 @@
         <v>4.75</v>
       </c>
       <c r="O185" t="n">
-        <v>0.0001251580510831528</v>
+        <v>0.0001341677690887891</v>
       </c>
       <c r="P185" t="n">
-        <v>89.89758690740086</v>
+        <v>89.78015265724214</v>
       </c>
       <c r="Q185" t="n">
         <v>-2.541280000000015</v>
@@ -13988,10 +13988,10 @@
         <v>0</v>
       </c>
       <c r="S185" t="n">
-        <v>76.08030797028809</v>
+        <v>57.06481338068163</v>
       </c>
       <c r="T185" t="n">
-        <v>76.08030797028809</v>
+        <v>57.06481338068163</v>
       </c>
     </row>
     <row r="186">
@@ -14050,10 +14050,10 @@
         <v>4.9</v>
       </c>
       <c r="O186" t="n">
-        <v>0.0001251580510831528</v>
+        <v>0.0001341677690887891</v>
       </c>
       <c r="P186" t="n">
-        <v>89.53290130005858</v>
+        <v>89.41455718850187</v>
       </c>
       <c r="Q186" t="n">
         <v>6.277199999999993</v>
@@ -14062,10 +14062,10 @@
         <v>0</v>
       </c>
       <c r="S186" t="n">
-        <v>81.91109019425001</v>
+        <v>62.90688281489936</v>
       </c>
       <c r="T186" t="n">
-        <v>81.91109019425001</v>
+        <v>62.90688281489936</v>
       </c>
     </row>
     <row r="187">
@@ -14124,10 +14124,10 @@
         <v>6.4</v>
       </c>
       <c r="O187" t="n">
-        <v>0.0001251580510831528</v>
+        <v>0.0001341677690887891</v>
       </c>
       <c r="P187" t="n">
-        <v>85.8860452266358</v>
+        <v>85.75860250109912</v>
       </c>
       <c r="Q187" t="n">
         <v>-5.848210000000009</v>
@@ -14136,10 +14136,10 @@
         <v>0</v>
       </c>
       <c r="S187" t="n">
-        <v>71.03258471127018</v>
+        <v>51.99985718009176</v>
       </c>
       <c r="T187" t="n">
-        <v>71.03258471127018</v>
+        <v>51.99985718009176</v>
       </c>
     </row>
     <row r="188">
@@ -14198,10 +14198,10 @@
         <v>10.4</v>
       </c>
       <c r="O188" t="n">
-        <v>0.0001251580510831528</v>
+        <v>0.0001341677690887891</v>
       </c>
       <c r="P188" t="n">
-        <v>76.16109569750839</v>
+        <v>76.00939000135848</v>
       </c>
       <c r="Q188" t="n">
         <v>1.867959999999982</v>
@@ -14210,10 +14210,10 @@
         <v>0</v>
       </c>
       <c r="S188" t="n">
-        <v>69.64708189132136</v>
+        <v>50.59475393962074</v>
       </c>
       <c r="T188" t="n">
-        <v>69.64708189132136</v>
+        <v>50.59475393962074</v>
       </c>
     </row>
     <row r="189">
@@ -14272,10 +14272,10 @@
         <v>13.9</v>
       </c>
       <c r="O189" t="n">
-        <v>0.0001251580510831528</v>
+        <v>0.0001341677690887891</v>
       </c>
       <c r="P189" t="n">
-        <v>67.6517648595219</v>
+        <v>67.47882906408543</v>
       </c>
       <c r="Q189" t="n">
         <v>-3.643590000000017</v>
@@ -14284,10 +14284,10 @@
         <v>0</v>
       </c>
       <c r="S189" t="n">
-        <v>59.97654828744953</v>
+        <v>40.88978437625305</v>
       </c>
       <c r="T189" t="n">
-        <v>59.97654828744953</v>
+        <v>40.88978437625305</v>
       </c>
     </row>
     <row r="190">
@@ -14346,10 +14346,10 @@
         <v>16.9</v>
       </c>
       <c r="O190" t="n">
-        <v>0.0001251580510831528</v>
+        <v>0.0001341677690887891</v>
       </c>
       <c r="P190" t="n">
-        <v>60.35805271267635</v>
+        <v>60.16691968927994</v>
       </c>
       <c r="Q190" t="n">
         <v>6.277199999999993</v>
@@ -14358,10 +14358,10 @@
         <v>0</v>
       </c>
       <c r="S190" t="n">
-        <v>61.78850610611151</v>
+        <v>42.6928684834129</v>
       </c>
       <c r="T190" t="n">
-        <v>61.78850610611151</v>
+        <v>42.6928684834129</v>
       </c>
     </row>
     <row r="191">
@@ -14420,10 +14420,10 @@
         <v>17.05</v>
       </c>
       <c r="O191" t="n">
-        <v>0.0001251580510831528</v>
+        <v>0.0001341677690887891</v>
       </c>
       <c r="P191" t="n">
-        <v>59.99336710533407</v>
+        <v>59.80132422053968</v>
       </c>
       <c r="Q191" t="n">
         <v>-10.25745000000001</v>
@@ -14432,10 +14432,10 @@
         <v>0</v>
       </c>
       <c r="S191" t="n">
-        <v>50.13263407051546</v>
+        <v>31.01254715421689</v>
       </c>
       <c r="T191" t="n">
-        <v>50.13263407051546</v>
+        <v>31.01254715421689</v>
       </c>
     </row>
     <row r="192">
@@ -14494,10 +14494,10 @@
         <v>20.05</v>
       </c>
       <c r="O192" t="n">
-        <v>0.0001251580510831528</v>
+        <v>0.0001341677690887891</v>
       </c>
       <c r="P192" t="n">
-        <v>52.7616530487755</v>
+        <v>52.55165545394903</v>
       </c>
       <c r="Q192" t="n">
         <v>-0.3366600000000091</v>
@@ -14564,10 +14564,10 @@
         <v>23.55</v>
       </c>
       <c r="O193" t="n">
-        <v>0.0001251580510831528</v>
+        <v>0.0001341677690887891</v>
       </c>
       <c r="P193" t="n">
-        <v>48.50698762978226</v>
+        <v>48.2863749853125</v>
       </c>
       <c r="Q193" t="n">
         <v>4.072579999999988</v>
@@ -14634,10 +14634,10 @@
         <v>24.3</v>
       </c>
       <c r="O194" t="n">
-        <v>0.0001251580510831528</v>
+        <v>0.0001341677690887891</v>
       </c>
       <c r="P194" t="n">
-        <v>47.59527361142656</v>
+        <v>47.37238631346182</v>
       </c>
       <c r="Q194" t="n">
         <v>-9.155140000000017</v>
@@ -14706,22 +14706,22 @@
         <v>0</v>
       </c>
       <c r="O195" t="n">
-        <v>3.071360663870742e-05</v>
+        <v>3.972332464434371e-05</v>
       </c>
       <c r="P195" t="n">
-        <v>103.5232069251498</v>
+        <v>103.4394867968696</v>
       </c>
       <c r="Q195" t="n">
         <v>1.867959999999982</v>
       </c>
       <c r="R195" t="n">
-        <v>3.578382247673588</v>
+        <v>0</v>
       </c>
       <c r="S195" t="n">
-        <v>90.93047547863998</v>
+        <v>69.55260548415224</v>
       </c>
       <c r="T195" t="n">
-        <v>90.93047547863998</v>
+        <v>69.55260548415224</v>
       </c>
     </row>
     <row r="196">
@@ -14780,22 +14780,22 @@
         <v>2.5</v>
       </c>
       <c r="O196" t="n">
-        <v>3.071360663870742e-05</v>
+        <v>3.972332464434371e-05</v>
       </c>
       <c r="P196" t="n">
-        <v>97.42661421445513</v>
+        <v>97.32768357538124</v>
       </c>
       <c r="Q196" t="n">
         <v>1.867959999999982</v>
       </c>
       <c r="R196" t="n">
-        <v>3.578382247673588</v>
+        <v>0</v>
       </c>
       <c r="S196" t="n">
-        <v>86.72551108594924</v>
+        <v>65.32853514979868</v>
       </c>
       <c r="T196" t="n">
-        <v>86.72551108594924</v>
+        <v>65.32853514979868</v>
       </c>
     </row>
     <row r="197">
@@ -14854,22 +14854,22 @@
         <v>4.5</v>
       </c>
       <c r="O197" t="n">
-        <v>3.071360663870742e-05</v>
+        <v>3.972332464434371e-05</v>
       </c>
       <c r="P197" t="n">
-        <v>92.54934004589937</v>
+        <v>92.43824099819057</v>
       </c>
       <c r="Q197" t="n">
         <v>1.867959999999982</v>
       </c>
       <c r="R197" t="n">
-        <v>3.578382247673588</v>
+        <v>0</v>
       </c>
       <c r="S197" t="n">
-        <v>83.36153957179664</v>
+        <v>61.94927888231582</v>
       </c>
       <c r="T197" t="n">
-        <v>83.36153957179664</v>
+        <v>61.94927888231582</v>
       </c>
     </row>
     <row r="198">
@@ -14928,22 +14928,22 @@
         <v>5.25</v>
       </c>
       <c r="O198" t="n">
-        <v>3.071360663870742e-05</v>
+        <v>3.972332464434371e-05</v>
       </c>
       <c r="P198" t="n">
-        <v>90.72036223269096</v>
+        <v>90.60470003174407</v>
       </c>
       <c r="Q198" t="n">
         <v>1.867959999999982</v>
       </c>
       <c r="R198" t="n">
-        <v>3.578382247673588</v>
+        <v>0</v>
       </c>
       <c r="S198" t="n">
-        <v>82.10005025398941</v>
+        <v>60.68205778200976</v>
       </c>
       <c r="T198" t="n">
-        <v>82.10005025398941</v>
+        <v>60.68205778200976</v>
       </c>
     </row>
     <row r="199">
@@ -15002,22 +15002,22 @@
         <v>5.75</v>
       </c>
       <c r="O199" t="n">
-        <v>3.071360663870742e-05</v>
+        <v>3.972332464434371e-05</v>
       </c>
       <c r="P199" t="n">
-        <v>89.50104369055202</v>
+        <v>89.38233938744641</v>
       </c>
       <c r="Q199" t="n">
         <v>1.867959999999982</v>
       </c>
       <c r="R199" t="n">
-        <v>3.578382247673588</v>
+        <v>0</v>
       </c>
       <c r="S199" t="n">
-        <v>81.25905737545126</v>
+        <v>59.83724371513904</v>
       </c>
       <c r="T199" t="n">
-        <v>81.25905737545126</v>
+        <v>59.83724371513904</v>
       </c>
     </row>
     <row r="200">
@@ -15076,22 +15076,22 @@
         <v>6.75</v>
       </c>
       <c r="O200" t="n">
-        <v>3.071360663870742e-05</v>
+        <v>3.972332464434371e-05</v>
       </c>
       <c r="P200" t="n">
-        <v>87.06240660627415</v>
+        <v>86.93761809885108</v>
       </c>
       <c r="Q200" t="n">
         <v>-1.438970000000012</v>
       </c>
       <c r="R200" t="n">
-        <v>3.578382247673588</v>
+        <v>0</v>
       </c>
       <c r="S200" t="n">
-        <v>77.29620367147611</v>
+        <v>55.86208635138713</v>
       </c>
       <c r="T200" t="n">
-        <v>77.29620367147611</v>
+        <v>55.86208635138713</v>
       </c>
     </row>
     <row r="201">
@@ -15150,22 +15150,22 @@
         <v>8.75</v>
       </c>
       <c r="O201" t="n">
-        <v>3.071360663870742e-05</v>
+        <v>3.972332464434371e-05</v>
       </c>
       <c r="P201" t="n">
-        <v>82.18513243771839</v>
+        <v>82.0481755216604</v>
       </c>
       <c r="Q201" t="n">
         <v>1.867959999999982</v>
       </c>
       <c r="R201" t="n">
-        <v>3.578382247673588</v>
+        <v>0</v>
       </c>
       <c r="S201" t="n">
-        <v>76.21310010422236</v>
+        <v>54.76835931391476</v>
       </c>
       <c r="T201" t="n">
-        <v>76.21310010422236</v>
+        <v>54.76835931391476</v>
       </c>
     </row>
     <row r="202">
@@ -15224,22 +15224,22 @@
         <v>8.779999999999999</v>
       </c>
       <c r="O202" t="n">
-        <v>3.071360663870742e-05</v>
+        <v>3.972332464434371e-05</v>
       </c>
       <c r="P202" t="n">
-        <v>82.11197332519006</v>
+        <v>81.97483388300255</v>
       </c>
       <c r="Q202" t="n">
         <v>-1.438970000000012</v>
       </c>
       <c r="R202" t="n">
-        <v>3.578382247673588</v>
+        <v>0</v>
       </c>
       <c r="S202" t="n">
-        <v>73.88177258461123</v>
+        <v>52.43214123989203</v>
       </c>
       <c r="T202" t="n">
-        <v>73.88177258461123</v>
+        <v>52.43214123989203</v>
       </c>
     </row>
     <row r="203">
@@ -15298,22 +15298,22 @@
         <v>14.78</v>
       </c>
       <c r="O203" t="n">
-        <v>3.071360663870742e-05</v>
+        <v>3.972332464434371e-05</v>
       </c>
       <c r="P203" t="n">
-        <v>67.48015081952279</v>
+        <v>67.30650615143054</v>
       </c>
       <c r="Q203" t="n">
         <v>1.867959999999982</v>
       </c>
       <c r="R203" t="n">
-        <v>3.578382247673588</v>
+        <v>0</v>
       </c>
       <c r="S203" t="n">
-        <v>66.07072598905229</v>
+        <v>44.57990166745395</v>
       </c>
       <c r="T203" t="n">
-        <v>66.07072598905229</v>
+        <v>44.57990166745395</v>
       </c>
     </row>
     <row r="204">
@@ -15372,22 +15372,22 @@
         <v>19.28</v>
       </c>
       <c r="O204" t="n">
-        <v>3.071360663870742e-05</v>
+        <v>3.972332464434371e-05</v>
       </c>
       <c r="P204" t="n">
-        <v>56.50628394027234</v>
+        <v>56.30526035275154</v>
       </c>
       <c r="Q204" t="n">
         <v>-1.438970000000012</v>
       </c>
       <c r="R204" t="n">
-        <v>3.578382247673588</v>
+        <v>0</v>
       </c>
       <c r="S204" t="n">
-        <v>56.2209221353101</v>
+        <v>34.69104583560705</v>
       </c>
       <c r="T204" t="n">
-        <v>56.2209221353101</v>
+        <v>34.69104583560705</v>
       </c>
     </row>
     <row r="205">
@@ -15446,16 +15446,16 @@
         <v>21.78</v>
       </c>
       <c r="O205" t="n">
-        <v>3.071360663870742e-05</v>
+        <v>3.972332464434371e-05</v>
       </c>
       <c r="P205" t="n">
-        <v>52.58037783194553</v>
+        <v>52.36964752794269</v>
       </c>
       <c r="Q205" t="n">
         <v>-1.438970000000012</v>
       </c>
       <c r="R205" t="n">
-        <v>3.578382247673588</v>
+        <v>0</v>
       </c>
       <c r="S205" t="inlineStr"/>
       <c r="T205" t="inlineStr"/>
@@ -15516,16 +15516,16 @@
         <v>30.28</v>
       </c>
       <c r="O206" t="n">
-        <v>3.071360663870742e-05</v>
+        <v>3.972332464434371e-05</v>
       </c>
       <c r="P206" t="n">
-        <v>42.21617022376455</v>
+        <v>41.97958205141252</v>
       </c>
       <c r="Q206" t="n">
         <v>-1.438970000000012</v>
       </c>
       <c r="R206" t="n">
-        <v>3.578382247673588</v>
+        <v>0</v>
       </c>
       <c r="S206" t="inlineStr"/>
       <c r="T206" t="inlineStr"/>
@@ -15588,22 +15588,22 @@
         <v>0</v>
       </c>
       <c r="O207" t="n">
-        <v>0.0001912407464298551</v>
+        <v>0.0001960459293661945</v>
       </c>
       <c r="P207" t="n">
-        <v>76.02199445100894</v>
+        <v>75.78134325439423</v>
       </c>
       <c r="Q207" t="n">
         <v>-3.643590000000017</v>
       </c>
       <c r="R207" t="n">
-        <v>3.578382247673588</v>
+        <v>0</v>
       </c>
       <c r="S207" t="n">
-        <v>68.25767005132174</v>
+        <v>46.6279278702271</v>
       </c>
       <c r="T207" t="n">
-        <v>68.25767005132174</v>
+        <v>46.6279278702271</v>
       </c>
     </row>
     <row r="208">
@@ -15662,22 +15662,22 @@
         <v>0.25</v>
       </c>
       <c r="O208" t="n">
-        <v>0.0001912407464298551</v>
+        <v>0.0001960459293661945</v>
       </c>
       <c r="P208" t="n">
-        <v>75.42614985633553</v>
+        <v>75.18401207515323</v>
       </c>
       <c r="Q208" t="n">
         <v>-3.643590000000017</v>
       </c>
       <c r="R208" t="n">
-        <v>3.578382247673588</v>
+        <v>0</v>
       </c>
       <c r="S208" t="n">
-        <v>67.84670192156891</v>
+        <v>46.21509243973661</v>
       </c>
       <c r="T208" t="n">
-        <v>67.84670192156891</v>
+        <v>46.21509243973661</v>
       </c>
     </row>
     <row r="209">
@@ -15736,22 +15736,22 @@
         <v>0.35</v>
       </c>
       <c r="O209" t="n">
-        <v>0.0001912407464298551</v>
+        <v>0.0001960459293661945</v>
       </c>
       <c r="P209" t="n">
-        <v>75.18781201846616</v>
+        <v>74.94507960345683</v>
       </c>
       <c r="Q209" t="n">
         <v>-1.438970000000012</v>
       </c>
       <c r="R209" t="n">
-        <v>3.578382247673588</v>
+        <v>0</v>
       </c>
       <c r="S209" t="n">
-        <v>69.2028933009337</v>
+        <v>47.57364442088074</v>
       </c>
       <c r="T209" t="n">
-        <v>69.2028933009337</v>
+        <v>47.57364442088074</v>
       </c>
     </row>
     <row r="210">
@@ -15810,22 +15810,22 @@
         <v>0.85</v>
       </c>
       <c r="O210" t="n">
-        <v>0.0001912407464298551</v>
+        <v>0.0001960459293661945</v>
       </c>
       <c r="P210" t="n">
-        <v>73.99612282911936</v>
+        <v>73.75041724497483</v>
       </c>
       <c r="Q210" t="n">
         <v>-2.541280000000015</v>
       </c>
       <c r="R210" t="n">
-        <v>3.578382247673588</v>
+        <v>0</v>
       </c>
       <c r="S210" t="n">
-        <v>67.62066772579509</v>
+        <v>45.98613048322957</v>
       </c>
       <c r="T210" t="n">
-        <v>67.62066772579509</v>
+        <v>45.98613048322957</v>
       </c>
     </row>
     <row r="211">
@@ -15884,22 +15884,22 @@
         <v>1.35</v>
       </c>
       <c r="O211" t="n">
-        <v>0.0001912407464298551</v>
+        <v>0.0001960459293661945</v>
       </c>
       <c r="P211" t="n">
-        <v>72.80443363977254</v>
+        <v>72.55575488649283</v>
       </c>
       <c r="Q211" t="n">
         <v>-2.541280000000015</v>
       </c>
       <c r="R211" t="n">
-        <v>3.578382247673588</v>
+        <v>0</v>
       </c>
       <c r="S211" t="n">
-        <v>66.79873146628942</v>
+        <v>45.16045962224859</v>
       </c>
       <c r="T211" t="n">
-        <v>66.79873146628942</v>
+        <v>45.16045962224859</v>
       </c>
     </row>
     <row r="212">
@@ -15958,22 +15958,22 @@
         <v>1.5</v>
       </c>
       <c r="O212" t="n">
-        <v>0.0001912407464298551</v>
+        <v>0.0001960459293661945</v>
       </c>
       <c r="P212" t="n">
-        <v>72.4469268829685</v>
+        <v>72.19735617894824</v>
       </c>
       <c r="Q212" t="n">
         <v>-5.848210000000009</v>
       </c>
       <c r="R212" t="n">
-        <v>3.578382247673588</v>
+        <v>0</v>
       </c>
       <c r="S212" t="n">
-        <v>64.27128264153886</v>
+        <v>42.62722913394381</v>
       </c>
       <c r="T212" t="n">
-        <v>64.27128264153886</v>
+        <v>42.62722913394381</v>
       </c>
     </row>
     <row r="213">
@@ -16032,22 +16032,22 @@
         <v>2.25</v>
       </c>
       <c r="O213" t="n">
-        <v>0.0001912407464298551</v>
+        <v>0.0001960459293661945</v>
       </c>
       <c r="P213" t="n">
-        <v>70.65939309894827</v>
+        <v>70.40536264122524</v>
       </c>
       <c r="Q213" t="n">
         <v>-5.848210000000009</v>
       </c>
       <c r="R213" t="n">
-        <v>3.578382247673588</v>
+        <v>0</v>
       </c>
       <c r="S213" t="n">
-        <v>63.03837825228037</v>
+        <v>41.38872284247232</v>
       </c>
       <c r="T213" t="n">
-        <v>63.03837825228037</v>
+        <v>41.38872284247232</v>
       </c>
     </row>
     <row r="214">
@@ -16106,22 +16106,22 @@
         <v>2.5</v>
       </c>
       <c r="O214" t="n">
-        <v>0.0001912407464298551</v>
+        <v>0.0001960459293661945</v>
       </c>
       <c r="P214" t="n">
-        <v>70.06354850427486</v>
+        <v>69.80803146198424</v>
       </c>
       <c r="Q214" t="n">
         <v>-1.438970000000012</v>
       </c>
       <c r="R214" t="n">
-        <v>3.578382247673588</v>
+        <v>0</v>
       </c>
       <c r="S214" t="n">
-        <v>65.66856738505936</v>
+        <v>44.02325971866247</v>
       </c>
       <c r="T214" t="n">
-        <v>65.66856738505936</v>
+        <v>44.02325971866247</v>
       </c>
     </row>
     <row r="215">
@@ -16180,22 +16180,22 @@
         <v>3.25</v>
       </c>
       <c r="O215" t="n">
-        <v>0.0001912407464298551</v>
+        <v>0.0001960459293661945</v>
       </c>
       <c r="P215" t="n">
-        <v>68.27601472025464</v>
+        <v>68.01603792426124</v>
       </c>
       <c r="Q215" t="n">
         <v>-2.541280000000015</v>
       </c>
       <c r="R215" t="n">
-        <v>3.578382247673588</v>
+        <v>0</v>
       </c>
       <c r="S215" t="n">
-        <v>63.67537368016792</v>
+        <v>42.02291035052082</v>
       </c>
       <c r="T215" t="n">
-        <v>63.67537368016792</v>
+        <v>42.02291035052082</v>
       </c>
     </row>
     <row r="216">
@@ -16254,22 +16254,22 @@
         <v>11.25</v>
       </c>
       <c r="O216" t="n">
-        <v>0.0001912407464298551</v>
+        <v>0.0001960459293661945</v>
       </c>
       <c r="P216" t="n">
-        <v>49.20898769070561</v>
+        <v>48.90144018854927</v>
       </c>
       <c r="Q216" t="n">
         <v>-1.438970000000012</v>
       </c>
       <c r="R216" t="n">
-        <v>3.578382247673588</v>
+        <v>0</v>
       </c>
       <c r="S216" t="n">
-        <v>51.28468284371036</v>
+        <v>29.57401965149511</v>
       </c>
       <c r="T216" t="n">
-        <v>51.28468284371036</v>
+        <v>29.57401965149511</v>
       </c>
     </row>
     <row r="217">
@@ -16328,16 +16328,16 @@
         <v>20.25</v>
       </c>
       <c r="O217" t="n">
-        <v>0.0001912407464298551</v>
+        <v>0.0001960459293661945</v>
       </c>
       <c r="P217" t="n">
-        <v>28.05832777604033</v>
+        <v>27.69805699503259</v>
       </c>
       <c r="Q217" t="n">
         <v>-2.541280000000015</v>
       </c>
       <c r="R217" t="n">
-        <v>3.578382247673588</v>
+        <v>0</v>
       </c>
       <c r="S217" t="inlineStr"/>
       <c r="T217" t="inlineStr"/>
@@ -16398,16 +16398,16 @@
         <v>30.25</v>
       </c>
       <c r="O218" t="n">
-        <v>0.0001912407464298551</v>
+        <v>0.0001960459293661945</v>
       </c>
       <c r="P218" t="n">
-        <v>16.14143588257219</v>
+        <v>15.75143341021261</v>
       </c>
       <c r="Q218" t="n">
         <v>-2.541280000000015</v>
       </c>
       <c r="R218" t="n">
-        <v>3.578382247673588</v>
+        <v>0</v>
       </c>
       <c r="S218" t="inlineStr"/>
       <c r="T218" t="inlineStr"/>
@@ -16468,16 +16468,16 @@
         <v>60.25</v>
       </c>
       <c r="O219" t="n">
-        <v>0.0001912407464298551</v>
+        <v>0.0001960459293661945</v>
       </c>
       <c r="P219" t="n">
-        <v>-19.60923979783225</v>
+        <v>-20.08843734424731</v>
       </c>
       <c r="Q219" t="n">
         <v>-2.541280000000015</v>
       </c>
       <c r="R219" t="n">
-        <v>3.578382247673588</v>
+        <v>0</v>
       </c>
       <c r="S219" t="inlineStr"/>
       <c r="T219" t="inlineStr"/>
@@ -16540,10 +16540,10 @@
         <v>0</v>
       </c>
       <c r="O220" t="n">
-        <v>-0.0006265580929149693</v>
+        <v>-0.0006241555014467997</v>
       </c>
       <c r="P220" t="n">
-        <v>118.4366564783529</v>
+        <v>118.4927861111011</v>
       </c>
       <c r="Q220" t="n">
         <v>10.68643999999998</v>
@@ -16552,10 +16552,10 @@
         <v>0</v>
       </c>
       <c r="S220" t="n">
-        <v>104.4341882999541</v>
+        <v>86.05118555540739</v>
       </c>
       <c r="T220" t="n">
-        <v>104.4341882999541</v>
+        <v>86.05118555540739</v>
       </c>
     </row>
     <row r="221">
@@ -16614,10 +16614,10 @@
         <v>1</v>
       </c>
       <c r="O221" t="n">
-        <v>-0.0006265580929149693</v>
+        <v>-0.0006241555014467997</v>
       </c>
       <c r="P221" t="n">
-        <v>116.5579694884159</v>
+        <v>116.6138994725702</v>
       </c>
       <c r="Q221" t="n">
         <v>-6.950520000000012</v>
@@ -16626,10 +16626,10 @@
         <v>0</v>
       </c>
       <c r="S221" t="n">
-        <v>90.97378433544905</v>
+        <v>72.56313532732148</v>
       </c>
       <c r="T221" t="n">
-        <v>90.97378433544905</v>
+        <v>72.56313532732148</v>
       </c>
     </row>
     <row r="222">
@@ -16688,10 +16688,10 @@
         <v>2.5</v>
       </c>
       <c r="O222" t="n">
-        <v>-0.0006265580929149693</v>
+        <v>-0.0006241555014467997</v>
       </c>
       <c r="P222" t="n">
-        <v>113.7399390035103</v>
+        <v>113.7955695147739</v>
       </c>
       <c r="Q222" t="n">
         <v>4.072579999999988</v>
@@ -16700,10 +16700,10 @@
         <v>0</v>
       </c>
       <c r="S222" t="n">
-        <v>96.63301512021194</v>
+        <v>78.2337245919781</v>
       </c>
       <c r="T222" t="n">
-        <v>96.63301512021194</v>
+        <v>78.2337245919781</v>
       </c>
     </row>
     <row r="223">
@@ -16762,10 +16762,10 @@
         <v>3.25</v>
       </c>
       <c r="O223" t="n">
-        <v>-0.0006265580929149693</v>
+        <v>-0.0006241555014467997</v>
       </c>
       <c r="P223" t="n">
-        <v>112.3309237610575</v>
+        <v>112.3864045358758</v>
       </c>
       <c r="Q223" t="n">
         <v>-5.848210000000009</v>
@@ -16774,10 +16774,10 @@
         <v>0</v>
       </c>
       <c r="S223" t="n">
-        <v>88.818580093732</v>
+        <v>70.40321615092414</v>
       </c>
       <c r="T223" t="n">
-        <v>88.818580093732</v>
+        <v>70.40321615092414</v>
       </c>
     </row>
     <row r="224">
@@ -16836,10 +16836,10 @@
         <v>3.5</v>
       </c>
       <c r="O224" t="n">
-        <v>-0.0006265580929149693</v>
+        <v>-0.0006241555014467997</v>
       </c>
       <c r="P224" t="n">
-        <v>111.8612520135733</v>
+        <v>111.9166828762431</v>
       </c>
       <c r="Q224" t="n">
         <v>-5.848210000000009</v>
@@ -16848,10 +16848,10 @@
         <v>0</v>
       </c>
       <c r="S224" t="n">
-        <v>88.49463636513755</v>
+        <v>70.07857590058332</v>
       </c>
       <c r="T224" t="n">
-        <v>88.49463636513755</v>
+        <v>70.07857590058332</v>
       </c>
     </row>
     <row r="225">
@@ -16910,10 +16910,10 @@
         <v>3.65</v>
       </c>
       <c r="O225" t="n">
-        <v>-0.0006265580929149693</v>
+        <v>-0.0006241555014467997</v>
       </c>
       <c r="P225" t="n">
-        <v>111.5794489650827</v>
+        <v>111.6348498804634</v>
       </c>
       <c r="Q225" t="n">
         <v>-4.745900000000006</v>
@@ -16922,10 +16922,10 @@
         <v>0</v>
       </c>
       <c r="S225" t="n">
-        <v>89.06055944361384</v>
+        <v>70.64563482704898</v>
       </c>
       <c r="T225" t="n">
-        <v>89.06055944361384</v>
+        <v>70.64563482704898</v>
       </c>
     </row>
     <row r="226">
@@ -16984,10 +16984,10 @@
         <v>3.75</v>
       </c>
       <c r="O226" t="n">
-        <v>-0.0006265580929149693</v>
+        <v>-0.0006241555014467997</v>
       </c>
       <c r="P226" t="n">
-        <v>111.391580266089</v>
+        <v>111.4469612166103</v>
       </c>
       <c r="Q226" t="n">
         <v>6.277199999999993</v>
@@ -16996,10 +16996,10 @@
         <v>0</v>
       </c>
       <c r="S226" t="n">
-        <v>96.53387510850561</v>
+        <v>78.13420949361426</v>
       </c>
       <c r="T226" t="n">
-        <v>96.53387510850561</v>
+        <v>78.13420949361426</v>
       </c>
     </row>
     <row r="227">
@@ -17058,10 +17058,10 @@
         <v>5.25</v>
       </c>
       <c r="O227" t="n">
-        <v>-0.0006265580929149693</v>
+        <v>-0.0006241555014467997</v>
       </c>
       <c r="P227" t="n">
-        <v>108.5735497811834</v>
+        <v>108.6286312588141</v>
       </c>
       <c r="Q227" t="n">
         <v>-3.643590000000017</v>
@@ -17070,10 +17070,10 @@
         <v>0</v>
       </c>
       <c r="S227" t="n">
-        <v>87.74760889624234</v>
+        <v>69.32978030153781</v>
       </c>
       <c r="T227" t="n">
-        <v>87.74760889624234</v>
+        <v>69.32978030153781</v>
       </c>
     </row>
     <row r="228">
@@ -17132,10 +17132,10 @@
         <v>5.75</v>
       </c>
       <c r="O228" t="n">
-        <v>-0.0006265580929149693</v>
+        <v>-0.0006241555014467997</v>
       </c>
       <c r="P228" t="n">
-        <v>107.6342062862149</v>
+        <v>107.6891879395486</v>
       </c>
       <c r="Q228" t="n">
         <v>2.970269999999999</v>
@@ -17144,10 +17144,10 @@
         <v>0</v>
       </c>
       <c r="S228" t="n">
-        <v>91.66145733285119</v>
+        <v>73.25155826087713</v>
       </c>
       <c r="T228" t="n">
-        <v>91.66145733285119</v>
+        <v>73.25155826087713</v>
       </c>
     </row>
     <row r="229">
@@ -17206,10 +17206,10 @@
         <v>9.25</v>
       </c>
       <c r="O229" t="n">
-        <v>-0.0006265580929149693</v>
+        <v>-0.0006241555014467997</v>
       </c>
       <c r="P229" t="n">
-        <v>101.0588018214352</v>
+        <v>101.1130847046906</v>
       </c>
       <c r="Q229" t="n">
         <v>-0.3366600000000091</v>
@@ -17218,10 +17218,10 @@
         <v>0</v>
       </c>
       <c r="S229" t="n">
-        <v>84.84537718563007</v>
+        <v>66.42106552609499</v>
       </c>
       <c r="T229" t="n">
-        <v>84.84537718563007</v>
+        <v>66.42106552609499</v>
       </c>
     </row>
     <row r="230">
@@ -17280,10 +17280,10 @@
         <v>11.25</v>
       </c>
       <c r="O230" t="n">
-        <v>-0.0006265580929149693</v>
+        <v>-0.0006241555014467997</v>
       </c>
       <c r="P230" t="n">
-        <v>97.30142784156114</v>
+        <v>97.35531142762889</v>
       </c>
       <c r="Q230" t="n">
         <v>4.072579999999988</v>
@@ -17292,10 +17292,10 @@
         <v>0</v>
       </c>
       <c r="S230" t="n">
-        <v>85.29498461940632</v>
+        <v>66.87131583004899</v>
       </c>
       <c r="T230" t="n">
-        <v>85.29498461940632</v>
+        <v>66.87131583004899</v>
       </c>
     </row>
     <row r="231">
@@ -17354,10 +17354,10 @@
         <v>11.75</v>
       </c>
       <c r="O231" t="n">
-        <v>-0.0006265580929149693</v>
+        <v>-0.0006241555014467997</v>
       </c>
       <c r="P231" t="n">
-        <v>96.36208434659261</v>
+        <v>96.41586810836345</v>
       </c>
       <c r="Q231" t="n">
         <v>5.174889999999976</v>
@@ -17366,10 +17366,10 @@
         <v>0</v>
       </c>
       <c r="S231" t="n">
-        <v>85.40738647785037</v>
+        <v>66.98387840603748</v>
       </c>
       <c r="T231" t="n">
-        <v>85.40738647785037</v>
+        <v>66.98387840603748</v>
       </c>
     </row>
     <row r="232">
@@ -17428,10 +17428,10 @@
         <v>12.5</v>
       </c>
       <c r="O232" t="n">
-        <v>-0.0006265580929149693</v>
+        <v>-0.0006241555014467997</v>
       </c>
       <c r="P232" t="n">
-        <v>94.95306910413983</v>
+        <v>95.00670312946531</v>
       </c>
       <c r="Q232" t="n">
         <v>4.072579999999988</v>
@@ -17440,10 +17440,10 @@
         <v>0</v>
       </c>
       <c r="S232" t="n">
-        <v>83.67526597643409</v>
+        <v>65.24811457834483</v>
       </c>
       <c r="T232" t="n">
-        <v>83.67526597643409</v>
+        <v>65.24811457834483</v>
       </c>
     </row>
     <row r="233">
@@ -17502,10 +17502,10 @@
         <v>14.25</v>
       </c>
       <c r="O233" t="n">
-        <v>-0.0006265580929149693</v>
+        <v>-0.0006241555014467997</v>
       </c>
       <c r="P233" t="n">
-        <v>91.66536687175</v>
+        <v>91.7186515120363</v>
       </c>
       <c r="Q233" t="n">
         <v>-2.541280000000015</v>
@@ -17514,10 +17514,10 @@
         <v>0</v>
       </c>
       <c r="S233" t="n">
-        <v>76.84592398247524</v>
+        <v>58.40457436593802</v>
       </c>
       <c r="T233" t="n">
-        <v>76.84592398247524</v>
+        <v>58.40457436593802</v>
       </c>
     </row>
     <row r="234">
@@ -17576,10 +17576,10 @@
         <v>14.75</v>
       </c>
       <c r="O234" t="n">
-        <v>-0.0006265580929149693</v>
+        <v>-0.0006241555014467997</v>
       </c>
       <c r="P234" t="n">
-        <v>90.72602337678147</v>
+        <v>90.77920819277088</v>
       </c>
       <c r="Q234" t="n">
         <v>7.379509999999982</v>
@@ -17588,10 +17588,10 @@
         <v>0</v>
       </c>
       <c r="S234" t="n">
-        <v>83.04064036598294</v>
+        <v>64.61188155528782</v>
       </c>
       <c r="T234" t="n">
-        <v>83.04064036598294</v>
+        <v>64.61188155528782</v>
       </c>
     </row>
     <row r="235">
@@ -17650,10 +17650,10 @@
         <v>15</v>
       </c>
       <c r="O235" t="n">
-        <v>-0.0006265580929149693</v>
+        <v>-0.0006241555014467997</v>
       </c>
       <c r="P235" t="n">
-        <v>90.2563516292972</v>
+        <v>90.30948653313817</v>
       </c>
       <c r="Q235" t="n">
         <v>9.584129999999988</v>
@@ -17662,10 +17662,10 @@
         <v>0</v>
       </c>
       <c r="S235" t="n">
-        <v>84.2372752686544</v>
+        <v>65.81092745828732</v>
       </c>
       <c r="T235" t="n">
-        <v>84.2372752686544</v>
+        <v>65.81092745828732</v>
       </c>
     </row>
     <row r="236">
@@ -17726,10 +17726,10 @@
         <v>0</v>
       </c>
       <c r="O236" t="n">
-        <v>0.0001912407464298551</v>
+        <v>0.0001960459293661945</v>
       </c>
       <c r="P236" t="n">
-        <v>87.07501357492654</v>
+        <v>87.178284186578</v>
       </c>
       <c r="Q236" t="n">
         <v>-8.052830000000014</v>
@@ -17738,10 +17738,10 @@
         <v>0</v>
       </c>
       <c r="S236" t="n">
-        <v>70.3719468819619</v>
+        <v>51.45736022321841</v>
       </c>
       <c r="T236" t="n">
-        <v>70.3719468819619</v>
+        <v>51.45736022321841</v>
       </c>
     </row>
     <row r="237">
@@ -17800,10 +17800,10 @@
         <v>0.75</v>
       </c>
       <c r="O237" t="n">
-        <v>0.0001912407464298551</v>
+        <v>0.0001960459293661945</v>
       </c>
       <c r="P237" t="n">
-        <v>85.71407378876918</v>
+        <v>85.81719977296751</v>
       </c>
       <c r="Q237" t="n">
         <v>6.277199999999993</v>
@@ -17812,10 +17812,10 @@
         <v>0</v>
       </c>
       <c r="S237" t="n">
-        <v>79.31703558029947</v>
+        <v>60.42062954555324</v>
       </c>
       <c r="T237" t="n">
-        <v>79.31703558029947</v>
+        <v>60.42062954555324</v>
       </c>
     </row>
     <row r="238">
@@ -17874,10 +17874,10 @@
         <v>1</v>
       </c>
       <c r="O238" t="n">
-        <v>0.0001912407464298551</v>
+        <v>0.0001960459293661945</v>
       </c>
       <c r="P238" t="n">
-        <v>85.26042719338339</v>
+        <v>85.36350496843069</v>
       </c>
       <c r="Q238" t="n">
         <v>-3.643590000000017</v>
@@ -17886,10 +17886,10 @@
         <v>0</v>
       </c>
       <c r="S238" t="n">
-        <v>72.16154093797259</v>
+        <v>53.25047829739602</v>
       </c>
       <c r="T238" t="n">
-        <v>72.16154093797259</v>
+        <v>53.25047829739602</v>
       </c>
     </row>
     <row r="239">
@@ -17948,10 +17948,10 @@
         <v>1.05</v>
       </c>
       <c r="O239" t="n">
-        <v>0.0001912407464298551</v>
+        <v>0.0001960459293661945</v>
       </c>
       <c r="P239" t="n">
-        <v>85.16969787430624</v>
+        <v>85.27276600752332</v>
       </c>
       <c r="Q239" t="n">
         <v>5.174889999999976</v>
@@ -17960,10 +17960,10 @@
         <v>0</v>
       </c>
       <c r="S239" t="n">
-        <v>78.18127730271017</v>
+        <v>59.28251019913215</v>
       </c>
       <c r="T239" t="n">
-        <v>78.18127730271017</v>
+        <v>59.28251019913215</v>
       </c>
     </row>
     <row r="240">
@@ -18022,10 +18022,10 @@
         <v>1.1</v>
       </c>
       <c r="O240" t="n">
-        <v>0.0001912407464298551</v>
+        <v>0.0001960459293661945</v>
       </c>
       <c r="P240" t="n">
-        <v>85.07896855522908</v>
+        <v>85.18202704661596</v>
       </c>
       <c r="Q240" t="n">
         <v>-3.643590000000017</v>
@@ -18034,10 +18034,10 @@
         <v>0</v>
       </c>
       <c r="S240" t="n">
-        <v>72.03638461732048</v>
+        <v>53.12505287414572</v>
       </c>
       <c r="T240" t="n">
-        <v>72.03638461732048</v>
+        <v>53.12505287414572</v>
       </c>
     </row>
     <row r="241">
@@ -18096,10 +18096,10 @@
         <v>1.2</v>
       </c>
       <c r="O241" t="n">
-        <v>0.0001912407464298551</v>
+        <v>0.0001960459293661945</v>
       </c>
       <c r="P241" t="n">
-        <v>84.89750991707476</v>
+        <v>85.00054912480122</v>
       </c>
       <c r="Q241" t="n">
         <v>2.970269999999999</v>
@@ -18108,10 +18108,10 @@
         <v>0</v>
       </c>
       <c r="S241" t="n">
-        <v>76.4729641904661</v>
+        <v>57.5706859109164</v>
       </c>
       <c r="T241" t="n">
-        <v>76.4729641904661</v>
+        <v>57.5706859109164</v>
       </c>
     </row>
     <row r="242">
@@ -18170,10 +18170,10 @@
         <v>2.2</v>
       </c>
       <c r="O242" t="n">
-        <v>0.0001912407464298551</v>
+        <v>0.0001960459293661945</v>
       </c>
       <c r="P242" t="n">
-        <v>83.08292353553162</v>
+        <v>83.1857699066539</v>
       </c>
       <c r="Q242" t="n">
         <v>-9.155140000000017</v>
@@ -18182,10 +18182,10 @@
         <v>0</v>
       </c>
       <c r="S242" t="n">
-        <v>66.85821851198243</v>
+        <v>47.93615783504156</v>
       </c>
       <c r="T242" t="n">
-        <v>66.85821851198243</v>
+        <v>47.93615783504156</v>
       </c>
     </row>
     <row r="243">
@@ -18244,10 +18244,10 @@
         <v>4.2</v>
       </c>
       <c r="O243" t="n">
-        <v>0.0001912407464298551</v>
+        <v>0.0001960459293661945</v>
       </c>
       <c r="P243" t="n">
-        <v>79.45375077244532</v>
+        <v>79.55621147035927</v>
       </c>
       <c r="Q243" t="n">
         <v>1.867959999999982</v>
@@ -18256,10 +18256,10 @@
         <v>0</v>
       </c>
       <c r="S243" t="n">
-        <v>71.95798525526969</v>
+        <v>53.04608013673711</v>
       </c>
       <c r="T243" t="n">
-        <v>71.95798525526969</v>
+        <v>53.04608013673711</v>
       </c>
     </row>
     <row r="244">
@@ -18318,10 +18318,10 @@
         <v>4.95</v>
       </c>
       <c r="O244" t="n">
-        <v>0.0001912407464298551</v>
+        <v>0.0001960459293661945</v>
       </c>
       <c r="P244" t="n">
-        <v>78.09281098628796</v>
+        <v>78.19512705674879</v>
       </c>
       <c r="Q244" t="n">
         <v>-1.438970000000012</v>
@@ -18330,10 +18330,10 @@
         <v>0</v>
       </c>
       <c r="S244" t="n">
-        <v>68.73844490347999</v>
+        <v>49.81986023234935</v>
       </c>
       <c r="T244" t="n">
-        <v>68.73844490347999</v>
+        <v>49.81986023234935</v>
       </c>
     </row>
     <row r="245">
@@ -18392,10 +18392,10 @@
         <v>4.98</v>
       </c>
       <c r="O245" t="n">
-        <v>0.0001912407464298551</v>
+        <v>0.0001960459293661945</v>
       </c>
       <c r="P245" t="n">
-        <v>78.03837339484166</v>
+        <v>78.14068368020438</v>
       </c>
       <c r="Q245" t="n">
         <v>6.277199999999993</v>
@@ -18404,10 +18404,10 @@
         <v>0</v>
       </c>
       <c r="S245" t="n">
-        <v>74.02292321671503</v>
+        <v>55.1151341420654</v>
       </c>
       <c r="T245" t="n">
-        <v>74.02292321671503</v>
+        <v>55.1151341420654</v>
       </c>
     </row>
     <row r="246">
@@ -18466,10 +18466,10 @@
         <v>5.08</v>
       </c>
       <c r="O246" t="n">
-        <v>0.0001912407464298551</v>
+        <v>0.0001960459293661945</v>
       </c>
       <c r="P246" t="n">
-        <v>77.85691475668735</v>
+        <v>77.95920575838964</v>
       </c>
       <c r="Q246" t="n">
         <v>-10.25745000000001</v>
@@ -18478,10 +18478,10 @@
         <v>0</v>
       </c>
       <c r="S246" t="n">
-        <v>62.4934271615686</v>
+        <v>43.56206256876267</v>
       </c>
       <c r="T246" t="n">
-        <v>62.4934271615686</v>
+        <v>43.56206256876267</v>
       </c>
     </row>
     <row r="247">
@@ -18540,10 +18540,10 @@
         <v>6.83</v>
       </c>
       <c r="O247" t="n">
-        <v>0.0001912407464298551</v>
+        <v>0.0001960459293661945</v>
       </c>
       <c r="P247" t="n">
-        <v>74.68138858898683</v>
+        <v>74.78334212663185</v>
       </c>
       <c r="Q247" t="n">
         <v>-10.25745000000001</v>
@@ -18552,10 +18552,10 @@
         <v>0</v>
       </c>
       <c r="S247" t="n">
-        <v>60.30319155015659</v>
+        <v>41.36711766188236</v>
       </c>
       <c r="T247" t="n">
-        <v>60.30319155015659</v>
+        <v>41.36711766188236</v>
       </c>
     </row>
     <row r="248">
@@ -18614,10 +18614,10 @@
         <v>6.88</v>
       </c>
       <c r="O248" t="n">
-        <v>0.0001912407464298551</v>
+        <v>0.0001960459293661945</v>
       </c>
       <c r="P248" t="n">
-        <v>74.59065926990968</v>
+        <v>74.69260316572448</v>
       </c>
       <c r="Q248" t="n">
         <v>4.072579999999988</v>
@@ -18626,10 +18626,10 @@
         <v>0</v>
       </c>
       <c r="S248" t="n">
-        <v>70.12437449305895</v>
+        <v>51.2083649469693</v>
       </c>
       <c r="T248" t="n">
-        <v>70.12437449305895</v>
+        <v>51.2083649469693</v>
       </c>
     </row>
     <row r="249">
@@ -18688,10 +18688,10 @@
         <v>8.129999999999999</v>
       </c>
       <c r="O249" t="n">
-        <v>0.0001912407464298551</v>
+        <v>0.0001960459293661945</v>
       </c>
       <c r="P249" t="n">
-        <v>72.32242629298074</v>
+        <v>72.42412914304035</v>
       </c>
       <c r="Q249" t="n">
         <v>-4.745900000000006</v>
@@ -18700,10 +18700,10 @@
         <v>0</v>
       </c>
       <c r="S249" t="n">
-        <v>62.47760595984388</v>
+        <v>43.54580254297922</v>
       </c>
       <c r="T249" t="n">
-        <v>62.47760595984388</v>
+        <v>43.54580254297922</v>
       </c>
     </row>
     <row r="250">
@@ -18762,10 +18762,10 @@
         <v>9.129999999999999</v>
       </c>
       <c r="O250" t="n">
-        <v>0.0001912407464298551</v>
+        <v>0.0001960459293661945</v>
       </c>
       <c r="P250" t="n">
-        <v>70.50783991143759</v>
+        <v>70.60934992489302</v>
       </c>
       <c r="Q250" t="n">
         <v>0.7656499999999937</v>
@@ -18774,10 +18774,10 @@
         <v>0</v>
       </c>
       <c r="S250" t="n">
-        <v>65.02748933148752</v>
+        <v>46.100763693827</v>
       </c>
       <c r="T250" t="n">
-        <v>65.02748933148752</v>
+        <v>46.100763693827</v>
       </c>
     </row>
     <row r="251">
@@ -18838,22 +18838,22 @@
         <v>0</v>
       </c>
       <c r="O251" t="n">
-        <v>0.0001912407464298551</v>
+        <v>0.0001960459293661945</v>
       </c>
       <c r="P251" t="n">
-        <v>98.86037664705644</v>
+        <v>98.96577453113304</v>
       </c>
       <c r="Q251" t="n">
         <v>-2.541280000000015</v>
       </c>
       <c r="R251" t="n">
-        <v>0.06967310904318857</v>
+        <v>0</v>
       </c>
       <c r="S251" t="n">
-        <v>82.35009270533722</v>
+        <v>63.41330194518144</v>
       </c>
       <c r="T251" t="n">
-        <v>82.35009270533722</v>
+        <v>63.41330194518144</v>
       </c>
     </row>
     <row r="252">
@@ -18912,22 +18912,22 @@
         <v>2.5</v>
       </c>
       <c r="O252" t="n">
-        <v>0.0001912407464298551</v>
+        <v>0.0001960459293661945</v>
       </c>
       <c r="P252" t="n">
-        <v>94.28598525435602</v>
+        <v>94.39089701657518</v>
       </c>
       <c r="Q252" t="n">
         <v>-5.848210000000009</v>
       </c>
       <c r="R252" t="n">
-        <v>0.06967310904318857</v>
+        <v>0</v>
       </c>
       <c r="S252" t="n">
-        <v>76.91415866868729</v>
+        <v>57.96592281715688</v>
       </c>
       <c r="T252" t="n">
-        <v>76.91415866868729</v>
+        <v>57.96592281715688</v>
       </c>
     </row>
     <row r="253">
@@ -18986,22 +18986,22 @@
         <v>3</v>
       </c>
       <c r="O253" t="n">
-        <v>0.0001912407464298551</v>
+        <v>0.0001960459293661945</v>
       </c>
       <c r="P253" t="n">
-        <v>93.37110697581593</v>
+        <v>93.47592151366361</v>
       </c>
       <c r="Q253" t="n">
         <v>1.867959999999982</v>
       </c>
       <c r="R253" t="n">
-        <v>0.06967310904318857</v>
+        <v>0</v>
       </c>
       <c r="S253" t="n">
-        <v>81.60517066016777</v>
+        <v>62.66645437424519</v>
       </c>
       <c r="T253" t="n">
-        <v>81.60517066016777</v>
+        <v>62.66645437424519</v>
       </c>
     </row>
     <row r="254">
@@ -19060,22 +19060,22 @@
         <v>4.25</v>
       </c>
       <c r="O254" t="n">
-        <v>0.0001912407464298551</v>
+        <v>0.0001960459293661945</v>
       </c>
       <c r="P254" t="n">
-        <v>91.08391127946574</v>
+        <v>91.18848275638467</v>
       </c>
       <c r="Q254" t="n">
         <v>-5.848210000000009</v>
       </c>
       <c r="R254" t="n">
-        <v>0.06967310904318857</v>
+        <v>0</v>
       </c>
       <c r="S254" t="n">
-        <v>74.70561240586157</v>
+        <v>55.75262788854701</v>
       </c>
       <c r="T254" t="n">
-        <v>74.70561240586157</v>
+        <v>55.75262788854701</v>
       </c>
     </row>
     <row r="255">
@@ -19134,22 +19134,22 @@
         <v>6.75</v>
       </c>
       <c r="O255" t="n">
-        <v>0.0001912407464298551</v>
+        <v>0.0001960459293661945</v>
       </c>
       <c r="P255" t="n">
-        <v>86.50951988676532</v>
+        <v>86.61360524182682</v>
       </c>
       <c r="Q255" t="n">
         <v>-1.438970000000012</v>
       </c>
       <c r="R255" t="n">
-        <v>0.06967310904318857</v>
+        <v>0</v>
       </c>
       <c r="S255" t="n">
-        <v>74.59170357864234</v>
+        <v>55.63815029721358</v>
       </c>
       <c r="T255" t="n">
-        <v>74.59170357864234</v>
+        <v>55.63815029721358</v>
       </c>
     </row>
     <row r="256">
@@ -19208,22 +19208,22 @@
         <v>8.25</v>
       </c>
       <c r="O256" t="n">
-        <v>0.0001912407464298551</v>
+        <v>0.0001960459293661945</v>
       </c>
       <c r="P256" t="n">
-        <v>83.76488505114506</v>
+        <v>83.86867873309211</v>
       </c>
       <c r="Q256" t="n">
         <v>-2.541280000000015</v>
       </c>
       <c r="R256" t="n">
-        <v>0.06967310904318857</v>
+        <v>0</v>
       </c>
       <c r="S256" t="n">
-        <v>71.93837460915874</v>
+        <v>52.97919728173497</v>
       </c>
       <c r="T256" t="n">
-        <v>71.93837460915874</v>
+        <v>52.97919728173497</v>
       </c>
     </row>
     <row r="257">
@@ -19282,16 +19282,16 @@
         <v>23.25</v>
       </c>
       <c r="O257" t="n">
-        <v>0.0001912407464298551</v>
+        <v>0.0001960459293661945</v>
       </c>
       <c r="P257" t="n">
-        <v>59.29329079623687</v>
+        <v>59.39451904799008</v>
       </c>
       <c r="Q257" t="n">
         <v>-8.052830000000014</v>
       </c>
       <c r="R257" t="n">
-        <v>0.06967310904318857</v>
+        <v>0</v>
       </c>
       <c r="S257" t="inlineStr"/>
       <c r="T257" t="inlineStr"/>
@@ -19354,10 +19354,10 @@
         <v>0</v>
       </c>
       <c r="O258" t="n">
-        <v>-0.0001109530600279567</v>
+        <v>-0.0001019433420223204</v>
       </c>
       <c r="P258" t="n">
-        <v>106.662887906308</v>
+        <v>106.5865767481407</v>
       </c>
       <c r="Q258" t="n">
         <v>-1.438970000000012</v>
@@ -19366,10 +19366,10 @@
         <v>0</v>
       </c>
       <c r="S258" t="n">
-        <v>88.26152847741855</v>
+        <v>69.44213471413411</v>
       </c>
       <c r="T258" t="n">
-        <v>88.26152847741855</v>
+        <v>69.44213471413411</v>
       </c>
     </row>
     <row r="259">
@@ -19428,10 +19428,10 @@
         <v>0.25</v>
       </c>
       <c r="O259" t="n">
-        <v>-0.0001109530600279567</v>
+        <v>-0.0001019433420223204</v>
       </c>
       <c r="P259" t="n">
-        <v>106.0504325360637</v>
+        <v>105.9725933507734</v>
       </c>
       <c r="Q259" t="n">
         <v>1.867959999999982</v>
@@ -19440,10 +19440,10 @@
         <v>0</v>
       </c>
       <c r="S259" t="n">
-        <v>90.11997144922076</v>
+        <v>71.30331961226453</v>
       </c>
       <c r="T259" t="n">
-        <v>90.11997144922076</v>
+        <v>71.30331961226453</v>
       </c>
     </row>
     <row r="260">
@@ -19502,10 +19502,10 @@
         <v>2.25</v>
       </c>
       <c r="O260" t="n">
-        <v>-0.0001109530600279567</v>
+        <v>-0.0001019433420223204</v>
       </c>
       <c r="P260" t="n">
-        <v>101.150789574109</v>
+        <v>101.0607261718348</v>
       </c>
       <c r="Q260" t="n">
         <v>1.867959999999982</v>
@@ -19514,10 +19514,10 @@
         <v>0</v>
       </c>
       <c r="S260" t="n">
-        <v>86.7405716484475</v>
+        <v>67.90856495722397</v>
       </c>
       <c r="T260" t="n">
-        <v>86.7405716484475</v>
+        <v>67.90856495722397</v>
       </c>
     </row>
     <row r="261">
@@ -19576,10 +19576,10 @@
         <v>3</v>
       </c>
       <c r="O261" t="n">
-        <v>-0.0001109530600279567</v>
+        <v>-0.0001019433420223204</v>
       </c>
       <c r="P261" t="n">
-        <v>99.31342346337594</v>
+        <v>99.21877597973287</v>
       </c>
       <c r="Q261" t="n">
         <v>1.867959999999982</v>
@@ -19588,10 +19588,10 @@
         <v>0</v>
       </c>
       <c r="S261" t="n">
-        <v>85.47329672315752</v>
+        <v>66.63553196158377</v>
       </c>
       <c r="T261" t="n">
-        <v>85.47329672315752</v>
+        <v>66.63553196158377</v>
       </c>
     </row>
     <row r="262">
@@ -19650,10 +19650,10 @@
         <v>7.5</v>
       </c>
       <c r="O262" t="n">
-        <v>-0.0001109530600279567</v>
+        <v>-0.0001019433420223204</v>
       </c>
       <c r="P262" t="n">
-        <v>88.28922679897785</v>
+        <v>88.16707482712108</v>
       </c>
       <c r="Q262" t="n">
         <v>1.867959999999982</v>
@@ -19662,10 +19662,10 @@
         <v>0</v>
       </c>
       <c r="S262" t="n">
-        <v>77.86964717141768</v>
+        <v>58.99733398774252</v>
       </c>
       <c r="T262" t="n">
-        <v>77.86964717141768</v>
+        <v>58.99733398774252</v>
       </c>
     </row>
     <row r="263">
@@ -19724,10 +19724,10 @@
         <v>11</v>
       </c>
       <c r="O263" t="n">
-        <v>-0.0001109530600279567</v>
+        <v>-0.0001019433420223204</v>
       </c>
       <c r="P263" t="n">
-        <v>79.71485161555711</v>
+        <v>79.57130726397858</v>
       </c>
       <c r="Q263" t="n">
         <v>1.867959999999982</v>
@@ -19736,10 +19736,10 @@
         <v>0</v>
       </c>
       <c r="S263" t="n">
-        <v>71.95569752006448</v>
+        <v>53.05651334142156</v>
       </c>
       <c r="T263" t="n">
-        <v>71.95569752006448</v>
+        <v>53.05651334142156</v>
       </c>
     </row>
     <row r="264">
@@ -19798,10 +19798,10 @@
         <v>11.75</v>
       </c>
       <c r="O264" t="n">
-        <v>-0.0001109530600279567</v>
+        <v>-0.0001019433420223204</v>
       </c>
       <c r="P264" t="n">
-        <v>77.87748550482409</v>
+        <v>77.72935707187661</v>
       </c>
       <c r="Q264" t="n">
         <v>1.867959999999982</v>
@@ -19810,10 +19810,10 @@
         <v>0</v>
       </c>
       <c r="S264" t="n">
-        <v>70.68842259477451</v>
+        <v>51.78348034578134</v>
       </c>
       <c r="T264" t="n">
-        <v>70.68842259477451</v>
+        <v>51.78348034578134</v>
       </c>
     </row>
     <row r="265">
@@ -19872,10 +19872,10 @@
         <v>31.75</v>
       </c>
       <c r="O265" t="n">
-        <v>-0.0001109530600279567</v>
+        <v>-0.0001019433420223204</v>
       </c>
       <c r="P265" t="n">
-        <v>43.27266982525963</v>
+        <v>43.03829365631136</v>
       </c>
       <c r="Q265" t="n">
         <v>-1.438970000000012</v>
